--- a/output/lisa_reconciliation.xlsx
+++ b/output/lisa_reconciliation.xlsx
@@ -16,7 +16,7 @@
     <sheet name="FOLLOW_UPS" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ACTION_QUEUE!$A$1:$AI$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ACTION_QUEUE!$A$1:$AI$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ALL_PO_LINES!$A$1:$AH$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DOCUMENTS!$A$1:$T$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">FOLLOW_UPS!$A$1:$E$11</definedName>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="399">
   <si>
     <t>Priority</t>
   </si>
@@ -231,6 +231,9 @@
     <t>PO-4500060619</t>
   </si>
   <si>
+    <t>APEX BAR &amp; TUBE CO.</t>
+  </si>
+  <si>
     <t>UNKNOWN_PO</t>
   </si>
   <si>
@@ -291,9 +294,6 @@
     <t>continental_01.pdf</t>
   </si>
   <si>
-    <t>CQH-41200</t>
-  </si>
-  <si>
     <t>PO-4500050012</t>
   </si>
   <si>
@@ -405,6 +405,24 @@
     <t>OST-220844</t>
   </si>
   <si>
+    <t>PO-4500050029</t>
+  </si>
+  <si>
+    <t>DATE_SEMANTICS_WARNING</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050029. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>SHIP_DATE</t>
+  </si>
+  <si>
+    <t>ostmark_02.pdf</t>
+  </si>
+  <si>
+    <t>OST-224427</t>
+  </si>
+  <si>
     <t>TOOL-INS-CAR</t>
   </si>
   <si>
@@ -417,6 +435,30 @@
     <t>Delivery window for PO-4500050027 line 2 straddles required date 2026-05-15. Ask Ostmark Werkzeug GmbH to commit a date on or before 2026-05-15.</t>
   </si>
   <si>
+    <t>PO-4500050028</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050028. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>ostmark_04.pdf</t>
+  </si>
+  <si>
+    <t>OST-226935</t>
+  </si>
+  <si>
+    <t>PO-4500050026</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050026. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>ostmark_03.pdf</t>
+  </si>
+  <si>
+    <t>OST-229377</t>
+  </si>
+  <si>
     <t>PO-4500050030</t>
   </si>
   <si>
@@ -426,18 +468,12 @@
     <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050030. Confirm whether the ship date will still meet the required date at Beacon.</t>
   </si>
   <si>
-    <t>SHIP_DATE</t>
-  </si>
-  <si>
     <t>quickship_02.pdf</t>
   </si>
   <si>
     <t>PO-4500050031</t>
   </si>
   <si>
-    <t>DATE_SEMANTICS_WARNING</t>
-  </si>
-  <si>
     <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050031. Confirm whether the ship date will still meet the required date at Beacon.</t>
   </si>
   <si>
@@ -543,51 +579,9 @@
     <t>continental_02.pdf</t>
   </si>
   <si>
-    <t>CQH-48302</t>
-  </si>
-  <si>
     <t>GREEN</t>
   </si>
   <si>
-    <t>PO-4500050029</t>
-  </si>
-  <si>
-    <t>Review PO-4500050029 line 1 with Ostmark Werkzeug GmbH.</t>
-  </si>
-  <si>
-    <t>ostmark_02.pdf</t>
-  </si>
-  <si>
-    <t>OST-224427</t>
-  </si>
-  <si>
-    <t>Review PO-4500050029 line 2 with Ostmark Werkzeug GmbH.</t>
-  </si>
-  <si>
-    <t>PO-4500050028</t>
-  </si>
-  <si>
-    <t>Review PO-4500050028 line 1 with Ostmark Werkzeug GmbH.</t>
-  </si>
-  <si>
-    <t>ostmark_04.pdf</t>
-  </si>
-  <si>
-    <t>OST-226935</t>
-  </si>
-  <si>
-    <t>PO-4500050026</t>
-  </si>
-  <si>
-    <t>Review PO-4500050026 line 1 with Ostmark Werkzeug GmbH.</t>
-  </si>
-  <si>
-    <t>ostmark_03.pdf</t>
-  </si>
-  <si>
-    <t>OST-229377</t>
-  </si>
-  <si>
     <t>BAR-A286-375</t>
   </si>
   <si>
@@ -849,10 +843,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>LOCAL_TEXT</t>
-  </si>
-  <si>
-    <t>local-parser-v1</t>
+    <t>NATIVE_TEXT</t>
+  </si>
+  <si>
+    <t>gpt-4o-mini</t>
   </si>
   <si>
     <t>Y</t>
@@ -885,10 +879,13 @@
     <t>171acbfe62b4</t>
   </si>
   <si>
-    <t>OCR_LOCAL</t>
-  </si>
-  <si>
-    <t>Extracted via OCR; native PDF text was empty</t>
+    <t>CONTINENTAL QUALITY HEAT TREAT</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>VISION</t>
   </si>
   <si>
     <t>bccc160e1d7a</t>
@@ -927,21 +924,12 @@
     <t>LIB-PO-9240</t>
   </si>
   <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>Split acknowledgment part 1 of 2</t>
-  </si>
-  <si>
     <t>liberty_02.pdf</t>
   </si>
   <si>
     <t>064f140583b6</t>
   </si>
   <si>
-    <t>Split acknowledgment part 2 of 2</t>
-  </si>
-  <si>
     <t>df73e325ff79</t>
   </si>
   <si>
@@ -954,6 +942,9 @@
     <t>e091bfef23ea</t>
   </si>
   <si>
+    <t>CAD</t>
+  </si>
+  <si>
     <t>e8a55dd92b82</t>
   </si>
   <si>
@@ -996,9 +987,6 @@
     <t>INVOICE</t>
   </si>
   <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
     <t>013b7d72a0f6</t>
   </si>
   <si>
@@ -1149,7 +1137,7 @@
     <t>LLM provider</t>
   </si>
   <si>
-    <t>local</t>
+    <t>openai</t>
   </si>
   <si>
     <t>LLM model</t>
@@ -1802,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -2272,7 +2260,7 @@
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>38</v>
@@ -2283,10 +2271,10 @@
         <v>40</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5">
@@ -2311,10 +2299,10 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="5"/>
       <c r="AF6" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH6" s="9">
         <v>46157</v>
@@ -2331,7 +2319,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2343,19 +2331,19 @@
         <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L7" s="5">
         <v>1000</v>
@@ -2418,10 +2406,10 @@
         <v>0.99</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" s="9">
         <v>46159</v>
@@ -2438,29 +2426,29 @@
         <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" s="5">
         <v>500</v>
@@ -2503,17 +2491,15 @@
         <v>21</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AE8" s="5">
         <v>0.6</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG8" s="4" t="s">
         <v>87</v>
       </c>
+      <c r="AG8" s="4"/>
       <c r="AH8" s="9">
         <v>46156</v>
       </c>
@@ -2655,7 +2641,7 @@
         <v>103</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>104</v>
@@ -2701,7 +2687,7 @@
         <v>7</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AE10" s="5">
         <v>0.55</v>
@@ -2905,10 +2891,10 @@
         <v>112</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>114</v>
@@ -2917,37 +2903,37 @@
         <v>115</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="H13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>128</v>
-      </c>
       <c r="L13" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="M13" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N13" s="5">
         <v>0</v>
       </c>
       <c r="O13" s="6">
-        <v>18.2</v>
+        <v>1240</v>
       </c>
       <c r="P13" s="11" t="s">
         <v>43</v>
       </c>
       <c r="Q13" s="6">
-        <v>16.744</v>
+        <v>1140.8</v>
       </c>
       <c r="R13" s="11" t="s">
         <v>120</v>
@@ -2956,47 +2942,49 @@
         <v>1.0902</v>
       </c>
       <c r="T13" s="6">
-        <v>18.254309</v>
+        <v>1243.70016</v>
       </c>
       <c r="U13" s="6">
-        <v>0.054309</v>
+        <v>3.70016</v>
       </c>
       <c r="V13" s="7">
-        <v>0.002984010989010989</v>
+        <v>0.002984</v>
       </c>
       <c r="W13" s="8">
-        <v>2.72</v>
+        <v>18.5</v>
       </c>
       <c r="X13" s="9">
-        <v>46157</v>
+        <v>46181</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="Z13" s="9">
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="AA13" s="9">
-        <v>46173</v>
+        <v>46181</v>
       </c>
       <c r="AB13" s="9">
-        <v>46173</v>
-      </c>
-      <c r="AC13" s="11"/>
+        <v>46181</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
       <c r="AD13" s="11" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="AE13" s="5">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AF13" s="11" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="AG13" s="11" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AH13" s="9">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="AI13" s="11" t="s">
         <v>46</v>
@@ -3010,98 +2998,100 @@
         <v>112</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L14" s="5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="M14" s="5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="N14" s="5">
         <v>0</v>
       </c>
       <c r="O14" s="6">
-        <v>0.18</v>
+        <v>18.2</v>
       </c>
       <c r="P14" s="11" t="s">
         <v>43</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.18</v>
+        <v>16.744</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S14" s="5">
-        <v>1</v>
+        <v>1.0902</v>
       </c>
       <c r="T14" s="6">
-        <v>0.18</v>
+        <v>18.254309</v>
       </c>
       <c r="U14" s="6">
-        <v>0</v>
+        <v>0.054309</v>
       </c>
       <c r="V14" s="7">
-        <v>0</v>
+        <v>0.002984010989010989</v>
       </c>
       <c r="W14" s="8">
-        <v>0</v>
+        <v>13.58</v>
       </c>
       <c r="X14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Z14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="AA14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="AB14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="AC14" s="2">
         <v>0</v>
       </c>
       <c r="AD14" s="11" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="5">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="AF14" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG14" s="11"/>
+        <v>129</v>
+      </c>
+      <c r="AG14" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AH14" s="9">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="AI14" s="11" t="s">
         <v>46</v>
@@ -3115,105 +3105,529 @@
         <v>112</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="L15" s="5">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="M15" s="5">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="N15" s="5">
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>0.06</v>
+        <v>18.2</v>
       </c>
       <c r="P15" s="11" t="s">
         <v>43</v>
       </c>
       <c r="Q15" s="6">
-        <v>0.06</v>
+        <v>16.744</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S15" s="5">
-        <v>1</v>
+        <v>1.0902</v>
       </c>
       <c r="T15" s="6">
-        <v>0.06</v>
+        <v>18.254309</v>
       </c>
       <c r="U15" s="6">
-        <v>0</v>
+        <v>0.054309</v>
       </c>
       <c r="V15" s="7">
-        <v>0</v>
+        <v>0.002984010989010989</v>
       </c>
       <c r="W15" s="8">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X15" s="9">
         <v>46157</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="Z15" s="9">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="AA15" s="9">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="AB15" s="9">
-        <v>46157</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>0</v>
-      </c>
+        <v>46173</v>
+      </c>
+      <c r="AC15" s="11"/>
       <c r="AD15" s="11" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="AE15" s="5">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="AF15" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG15" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="AG15" s="11" t="s">
+        <v>124</v>
+      </c>
       <c r="AH15" s="9">
-        <v>46152</v>
+        <v>46143</v>
       </c>
       <c r="AI15" s="11" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="16" spans="1:35" ht="32" customHeight="1">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L16" s="5">
+        <v>5</v>
+      </c>
+      <c r="M16" s="5">
+        <v>5</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <v>1240</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>1140.8</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="S16" s="5">
+        <v>1.0874</v>
+      </c>
+      <c r="T16" s="6">
+        <v>1240.50592</v>
+      </c>
+      <c r="U16" s="6">
+        <v>0.50592</v>
+      </c>
+      <c r="V16" s="7">
+        <v>0.000408</v>
+      </c>
+      <c r="W16" s="8">
+        <v>2.53</v>
+      </c>
+      <c r="X16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="AF16" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH16" s="9">
+        <v>46142</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" ht="32" customHeight="1">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="5">
+        <v>250</v>
+      </c>
+      <c r="M17" s="5">
+        <v>250</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <v>18.2</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>16.744</v>
+      </c>
+      <c r="R17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="S17" s="5">
+        <v>1.0874</v>
+      </c>
+      <c r="T17" s="6">
+        <v>18.207426</v>
+      </c>
+      <c r="U17" s="6">
+        <v>0.007426</v>
+      </c>
+      <c r="V17" s="7">
+        <v>0.000408021978021978</v>
+      </c>
+      <c r="W17" s="8">
+        <v>1.86</v>
+      </c>
+      <c r="X17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="Y17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="AF17" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG17" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH17" s="9">
+        <v>46142</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" ht="32" customHeight="1">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="L18" s="5">
+        <v>500</v>
+      </c>
+      <c r="M18" s="5">
+        <v>500</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" s="5">
+        <v>1</v>
+      </c>
+      <c r="T18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="U18" s="6">
+        <v>0</v>
+      </c>
+      <c r="V18" s="7">
+        <v>0</v>
+      </c>
+      <c r="W18" s="8">
+        <v>0</v>
+      </c>
+      <c r="X18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="Y18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE18" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="AF18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG18" s="11"/>
+      <c r="AH18" s="9">
+        <v>46153</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" ht="32" customHeight="1">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="L19" s="5">
+        <v>500</v>
+      </c>
+      <c r="M19" s="5">
+        <v>500</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" s="5">
+        <v>1</v>
+      </c>
+      <c r="T19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="U19" s="6">
+        <v>0</v>
+      </c>
+      <c r="V19" s="7">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="Y19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="AF19" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG19" s="11"/>
+      <c r="AH19" s="9">
+        <v>46152</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI15"/>
+  <autoFilter ref="A1:AI19"/>
   <hyperlinks>
     <hyperlink ref="AF2" r:id="rId1"/>
     <hyperlink ref="AF3" r:id="rId2"/>
@@ -3229,6 +3643,10 @@
     <hyperlink ref="AF13" r:id="rId12"/>
     <hyperlink ref="AF14" r:id="rId13"/>
     <hyperlink ref="AF15" r:id="rId14"/>
+    <hyperlink ref="AF16" r:id="rId15"/>
+    <hyperlink ref="AF17" r:id="rId16"/>
+    <hyperlink ref="AF18" r:id="rId17"/>
+    <hyperlink ref="AF19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3688,7 +4106,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>38</v>
@@ -3699,10 +4117,10 @@
         <v>40</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5">
@@ -3727,10 +4145,10 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG6" s="9">
         <v>46157</v>
@@ -3744,7 +4162,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -3756,19 +4174,19 @@
         <v>38</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="5">
         <v>1000</v>
@@ -3831,10 +4249,10 @@
         <v>0.99</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG7" s="9">
         <v>46159</v>
@@ -3848,29 +4266,29 @@
         <v>35</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" s="5">
         <v>500</v>
@@ -3913,17 +4331,15 @@
         <v>21</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD8" s="5">
         <v>0.6</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF8" s="4" t="s">
         <v>87</v>
       </c>
+      <c r="AF8" s="4"/>
       <c r="AG8" s="9">
         <v>46156</v>
       </c>
@@ -4059,7 +4475,7 @@
         <v>103</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>104</v>
@@ -4105,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD10" s="5">
         <v>0.55</v>
@@ -4300,10 +4716,10 @@
         <v>112</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>114</v>
@@ -4312,37 +4728,37 @@
         <v>115</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="G13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="J13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>128</v>
-      </c>
       <c r="K13" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
       </c>
       <c r="N13" s="6">
-        <v>18.2</v>
+        <v>1240</v>
       </c>
       <c r="O13" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P13" s="6">
-        <v>16.744</v>
+        <v>1140.8</v>
       </c>
       <c r="Q13" s="11" t="s">
         <v>120</v>
@@ -4351,47 +4767,49 @@
         <v>1.0902</v>
       </c>
       <c r="S13" s="6">
-        <v>18.254309</v>
+        <v>1243.70016</v>
       </c>
       <c r="T13" s="6">
-        <v>0.054309</v>
+        <v>3.70016</v>
       </c>
       <c r="U13" s="7">
-        <v>0.002984010989010989</v>
+        <v>0.002984</v>
       </c>
       <c r="V13" s="8">
-        <v>2.72</v>
+        <v>18.5</v>
       </c>
       <c r="W13" s="9">
-        <v>46157</v>
+        <v>46181</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="Y13" s="9">
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="Z13" s="9">
-        <v>46173</v>
+        <v>46181</v>
       </c>
       <c r="AA13" s="9">
-        <v>46173</v>
-      </c>
-      <c r="AB13" s="11"/>
+        <v>46181</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
       <c r="AC13" s="11" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="AD13" s="5">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AE13" s="11" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="AF13" s="11" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG13" s="9">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="AH13" s="11" t="s">
         <v>46</v>
@@ -4402,98 +4820,100 @@
         <v>112</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K14" s="5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L14" s="5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <v>0.18</v>
+        <v>18.2</v>
       </c>
       <c r="O14" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P14" s="6">
-        <v>0.18</v>
+        <v>16.744</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="R14" s="5">
-        <v>1</v>
+        <v>1.0902</v>
       </c>
       <c r="S14" s="6">
-        <v>0.18</v>
+        <v>18.254309</v>
       </c>
       <c r="T14" s="6">
-        <v>0</v>
+        <v>0.054309</v>
       </c>
       <c r="U14" s="7">
-        <v>0</v>
+        <v>0.002984010989010989</v>
       </c>
       <c r="V14" s="8">
-        <v>0</v>
+        <v>13.58</v>
       </c>
       <c r="W14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Y14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="Z14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="AA14" s="9">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="AB14" s="2">
         <v>0</v>
       </c>
       <c r="AC14" s="11" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="AD14" s="5">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="AE14" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF14" s="11"/>
+        <v>129</v>
+      </c>
+      <c r="AF14" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AG14" s="9">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="AH14" s="11" t="s">
         <v>46</v>
@@ -4504,495 +4924,555 @@
         <v>112</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="K15" s="5">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L15" s="5">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="6">
-        <v>0.06</v>
+        <v>18.2</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P15" s="6">
-        <v>0.06</v>
+        <v>16.744</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="R15" s="5">
-        <v>1</v>
+        <v>1.0902</v>
       </c>
       <c r="S15" s="6">
-        <v>0.06</v>
+        <v>18.254309</v>
       </c>
       <c r="T15" s="6">
-        <v>0</v>
+        <v>0.054309</v>
       </c>
       <c r="U15" s="7">
-        <v>0</v>
+        <v>0.002984010989010989</v>
       </c>
       <c r="V15" s="8">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="W15" s="9">
         <v>46157</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="Y15" s="9">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="Z15" s="9">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="AA15" s="9">
-        <v>46157</v>
-      </c>
-      <c r="AB15" s="2">
-        <v>0</v>
-      </c>
+        <v>46173</v>
+      </c>
+      <c r="AB15" s="11"/>
       <c r="AC15" s="11" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="AD15" s="5">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="AE15" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF15" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="AF15" s="11" t="s">
+        <v>124</v>
+      </c>
       <c r="AG15" s="9">
-        <v>46152</v>
+        <v>46143</v>
       </c>
       <c r="AH15" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="28" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="5">
+        <v>5</v>
+      </c>
+      <c r="L16" s="5">
+        <v>5</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <v>1240</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P16" s="6">
+        <v>1140.8</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="R16" s="5">
+        <v>1.0874</v>
+      </c>
+      <c r="S16" s="6">
+        <v>1240.50592</v>
+      </c>
+      <c r="T16" s="6">
+        <v>0.50592</v>
+      </c>
+      <c r="U16" s="7">
+        <v>0.000408</v>
+      </c>
+      <c r="V16" s="8">
+        <v>2.53</v>
+      </c>
+      <c r="W16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>46186</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF16" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="AG16" s="9">
+        <v>46142</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" ht="28" customHeight="1">
+      <c r="A17" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13" t="s">
+      <c r="K17" s="5">
+        <v>250</v>
+      </c>
+      <c r="L17" s="5">
+        <v>250</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <v>18.2</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="6">
+        <v>16.744</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="R17" s="5">
+        <v>1.0874</v>
+      </c>
+      <c r="S17" s="6">
+        <v>18.207426</v>
+      </c>
+      <c r="T17" s="6">
+        <v>0.007426</v>
+      </c>
+      <c r="U17" s="7">
+        <v>0.000408021978021978</v>
+      </c>
+      <c r="V17" s="8">
+        <v>1.86</v>
+      </c>
+      <c r="W17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>46205</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="AE17" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="AF17" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="AG17" s="9">
+        <v>46142</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="28" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="K16" s="5">
-        <v>2500</v>
-      </c>
-      <c r="L16" s="5">
-        <v>2500</v>
-      </c>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="O16" s="13" t="s">
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="K18" s="5">
+        <v>500</v>
+      </c>
+      <c r="L18" s="5">
+        <v>500</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="O18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="9">
-        <v>46170</v>
-      </c>
-      <c r="X16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y16" s="9">
-        <v>46170</v>
-      </c>
-      <c r="Z16" s="9">
-        <v>46170</v>
-      </c>
-      <c r="AA16" s="9">
-        <v>46170</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD16" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="AE16" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF16" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG16" s="9">
+      <c r="P18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1</v>
+      </c>
+      <c r="S18" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="T18" s="6">
+        <v>0</v>
+      </c>
+      <c r="U18" s="7">
+        <v>0</v>
+      </c>
+      <c r="V18" s="8">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>46163</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF18" s="11"/>
+      <c r="AG18" s="9">
+        <v>46153</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" ht="28" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K19" s="5">
+        <v>500</v>
+      </c>
+      <c r="L19" s="5">
+        <v>500</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="R19" s="5">
+        <v>1</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="T19" s="6">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7">
+        <v>0</v>
+      </c>
+      <c r="V19" s="8">
+        <v>0</v>
+      </c>
+      <c r="W19" s="9">
         <v>46157</v>
       </c>
-      <c r="AH16" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" ht="28" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="K17" s="5">
-        <v>2500</v>
-      </c>
-      <c r="L17" s="5">
-        <v>2500</v>
-      </c>
-      <c r="M17" s="5">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="9">
-        <v>46161</v>
-      </c>
-      <c r="X17" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y17" s="9">
-        <v>46161</v>
-      </c>
-      <c r="Z17" s="9">
-        <v>46161</v>
-      </c>
-      <c r="AA17" s="9">
-        <v>46161</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="AE17" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF17" s="13" t="s">
+      <c r="X19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="AE19" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="AG17" s="9">
-        <v>46156</v>
-      </c>
-      <c r="AH17" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" ht="28" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="K18" s="5">
-        <v>10000</v>
-      </c>
-      <c r="L18" s="5">
-        <v>10000</v>
-      </c>
-      <c r="M18" s="5">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="9">
-        <v>46159</v>
-      </c>
-      <c r="X18" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y18" s="9">
-        <v>46159</v>
-      </c>
-      <c r="Z18" s="9">
-        <v>46159</v>
-      </c>
-      <c r="AA18" s="9">
-        <v>46159</v>
-      </c>
-      <c r="AB18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD18" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="AE18" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="AF18" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG18" s="9">
-        <v>46156</v>
-      </c>
-      <c r="AH18" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" ht="28" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K19" s="5">
-        <v>2500</v>
-      </c>
-      <c r="L19" s="5">
-        <v>2500</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="9">
-        <v>46155</v>
-      </c>
-      <c r="X19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y19" s="9">
-        <v>46155</v>
-      </c>
-      <c r="Z19" s="9">
-        <v>46155</v>
-      </c>
-      <c r="AA19" s="9">
-        <v>46155</v>
-      </c>
-      <c r="AB19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD19" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="AE19" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF19" s="13" t="s">
-        <v>157</v>
-      </c>
+      <c r="AF19" s="11"/>
       <c r="AG19" s="9">
         <v>46152</v>
       </c>
-      <c r="AH19" s="13" t="s">
+      <c r="AH19" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="28" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K20" s="5">
-        <v>750</v>
+        <v>2500</v>
       </c>
       <c r="L20" s="5">
-        <v>750</v>
+        <v>2500</v>
       </c>
       <c r="M20" s="5">
         <v>0</v>
       </c>
       <c r="N20" s="6">
-        <v>2.4</v>
+        <v>0.11</v>
       </c>
       <c r="O20" s="13" t="s">
         <v>43</v>
@@ -5005,37 +5485,37 @@
       <c r="U20" s="7"/>
       <c r="V20" s="8"/>
       <c r="W20" s="9">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="X20" s="13" t="s">
         <v>50</v>
       </c>
       <c r="Y20" s="9">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="Z20" s="9">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="AA20" s="9">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="AB20" s="2">
         <v>0</v>
       </c>
       <c r="AC20" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD20" s="5">
         <v>0.6</v>
       </c>
       <c r="AE20" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AF20" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG20" s="9">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="AH20" s="13" t="s">
         <v>46</v>
@@ -5043,44 +5523,44 @@
     </row>
     <row r="21" spans="1:34" ht="28" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="K21" s="5">
-        <v>350</v>
+        <v>2500</v>
       </c>
       <c r="L21" s="5">
-        <v>350</v>
+        <v>2500</v>
       </c>
       <c r="M21" s="5">
         <v>0</v>
       </c>
       <c r="N21" s="6">
-        <v>3.1</v>
+        <v>0.11</v>
       </c>
       <c r="O21" s="13" t="s">
         <v>43</v>
@@ -5093,37 +5573,37 @@
       <c r="U21" s="7"/>
       <c r="V21" s="8"/>
       <c r="W21" s="9">
-        <v>46151</v>
+        <v>46161</v>
       </c>
       <c r="X21" s="13" t="s">
         <v>50</v>
       </c>
       <c r="Y21" s="9">
-        <v>46151</v>
+        <v>46161</v>
       </c>
       <c r="Z21" s="9">
-        <v>46151</v>
+        <v>46161</v>
       </c>
       <c r="AA21" s="9">
-        <v>46151</v>
+        <v>46161</v>
       </c>
       <c r="AB21" s="2">
         <v>0</v>
       </c>
       <c r="AC21" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD21" s="5">
         <v>0.6</v>
       </c>
       <c r="AE21" s="13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AF21" s="13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG21" s="9">
-        <v>46158</v>
+        <v>46156</v>
       </c>
       <c r="AH21" s="13" t="s">
         <v>46</v>
@@ -5131,44 +5611,44 @@
     </row>
     <row r="22" spans="1:34" ht="28" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K22" s="5">
-        <v>350</v>
+        <v>10000</v>
       </c>
       <c r="L22" s="5">
-        <v>350</v>
+        <v>10000</v>
       </c>
       <c r="M22" s="5">
         <v>0</v>
       </c>
       <c r="N22" s="6">
-        <v>3.1</v>
+        <v>0.11</v>
       </c>
       <c r="O22" s="13" t="s">
         <v>43</v>
@@ -5181,34 +5661,34 @@
       <c r="U22" s="7"/>
       <c r="V22" s="8"/>
       <c r="W22" s="9">
-        <v>46149</v>
+        <v>46159</v>
       </c>
       <c r="X22" s="13" t="s">
         <v>50</v>
       </c>
       <c r="Y22" s="9">
-        <v>46149</v>
+        <v>46159</v>
       </c>
       <c r="Z22" s="9">
-        <v>46149</v>
+        <v>46159</v>
       </c>
       <c r="AA22" s="9">
-        <v>46149</v>
+        <v>46159</v>
       </c>
       <c r="AB22" s="2">
         <v>0</v>
       </c>
       <c r="AC22" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD22" s="5">
         <v>0.6</v>
       </c>
       <c r="AE22" s="13" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AF22" s="13" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AG22" s="9">
         <v>46156</v>
@@ -5218,416 +5698,358 @@
       </c>
     </row>
     <row r="23" spans="1:34" ht="28" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="K23" s="5">
+        <v>2500</v>
+      </c>
+      <c r="L23" s="5">
+        <v>2500</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="9">
+        <v>46155</v>
+      </c>
+      <c r="X23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y23" s="9">
+        <v>46155</v>
+      </c>
+      <c r="Z23" s="9">
+        <v>46155</v>
+      </c>
+      <c r="AA23" s="9">
+        <v>46155</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD23" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="AE23" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF23" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG23" s="9">
+        <v>46152</v>
+      </c>
+      <c r="AH23" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" ht="28" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="5">
+        <v>750</v>
+      </c>
+      <c r="L24" s="5">
+        <v>750</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="9">
+        <v>46165</v>
+      </c>
+      <c r="X24" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y24" s="9">
+        <v>46165</v>
+      </c>
+      <c r="Z24" s="9">
+        <v>46165</v>
+      </c>
+      <c r="AA24" s="9">
+        <v>46165</v>
+      </c>
+      <c r="AB24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="AE24" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="AF24" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15" t="s">
+      <c r="AG24" s="9">
+        <v>46154</v>
+      </c>
+      <c r="AH24" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" ht="28" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="K23" s="5">
-        <v>5</v>
-      </c>
-      <c r="L23" s="5">
-        <v>5</v>
-      </c>
-      <c r="M23" s="5">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <v>1240</v>
-      </c>
-      <c r="O23" s="15" t="s">
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="5">
+        <v>350</v>
+      </c>
+      <c r="L25" s="5">
+        <v>350</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="O25" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="P23" s="6">
-        <v>1140.8</v>
-      </c>
-      <c r="Q23" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="R23" s="5">
-        <v>1.0902</v>
-      </c>
-      <c r="S23" s="6">
-        <v>1243.70016</v>
-      </c>
-      <c r="T23" s="6">
-        <v>3.70016</v>
-      </c>
-      <c r="U23" s="7">
-        <v>0.002984</v>
-      </c>
-      <c r="V23" s="8">
-        <v>18.5</v>
-      </c>
-      <c r="W23" s="9">
-        <v>46181</v>
-      </c>
-      <c r="X23" s="15" t="s">
+      <c r="P25" s="6"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="9">
+        <v>46151</v>
+      </c>
+      <c r="X25" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="Y23" s="9">
-        <v>46181</v>
-      </c>
-      <c r="Z23" s="9">
-        <v>46181</v>
-      </c>
-      <c r="AA23" s="9">
-        <v>46181</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD23" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="AE23" s="15" t="s">
+      <c r="Y25" s="9">
+        <v>46151</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>46151</v>
+      </c>
+      <c r="AA25" s="9">
+        <v>46151</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD25" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="AE25" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="AF25" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG25" s="9">
+        <v>46158</v>
+      </c>
+      <c r="AH25" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" ht="28" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AF23" s="15" t="s">
+      <c r="G26" s="13"/>
+      <c r="H26" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AG23" s="9">
+      <c r="I26" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="K26" s="5">
+        <v>350</v>
+      </c>
+      <c r="L26" s="5">
+        <v>350</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="9">
         <v>46149</v>
       </c>
-      <c r="AH23" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:34" ht="28" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" s="5">
-        <v>250</v>
-      </c>
-      <c r="L24" s="5">
-        <v>250</v>
-      </c>
-      <c r="M24" s="5">
-        <v>0</v>
-      </c>
-      <c r="N24" s="6">
-        <v>18.2</v>
-      </c>
-      <c r="O24" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="P24" s="6">
-        <v>16.744</v>
-      </c>
-      <c r="Q24" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="R24" s="5">
-        <v>1.0902</v>
-      </c>
-      <c r="S24" s="6">
-        <v>18.254309</v>
-      </c>
-      <c r="T24" s="6">
-        <v>0.054309</v>
-      </c>
-      <c r="U24" s="7">
-        <v>0.002984010989010989</v>
-      </c>
-      <c r="V24" s="8">
-        <v>13.58</v>
-      </c>
-      <c r="W24" s="9">
-        <v>46181</v>
-      </c>
-      <c r="X24" s="15" t="s">
+      <c r="X26" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="Y24" s="9">
-        <v>46181</v>
-      </c>
-      <c r="Z24" s="9">
-        <v>46181</v>
-      </c>
-      <c r="AA24" s="9">
-        <v>46181</v>
-      </c>
-      <c r="AB24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD24" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="AE24" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF24" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG24" s="9">
+      <c r="Y26" s="9">
         <v>46149</v>
       </c>
-      <c r="AH24" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34" ht="28" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="K25" s="5">
-        <v>5</v>
-      </c>
-      <c r="L25" s="5">
-        <v>5</v>
-      </c>
-      <c r="M25" s="5">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
-        <v>1240</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="P25" s="6">
-        <v>1140.8</v>
-      </c>
-      <c r="Q25" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="R25" s="5">
-        <v>1.0874</v>
-      </c>
-      <c r="S25" s="6">
-        <v>1240.50592</v>
-      </c>
-      <c r="T25" s="6">
-        <v>0.50592</v>
-      </c>
-      <c r="U25" s="7">
-        <v>0.000408</v>
-      </c>
-      <c r="V25" s="8">
-        <v>2.53</v>
-      </c>
-      <c r="W25" s="9">
-        <v>46186</v>
-      </c>
-      <c r="X25" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y25" s="9">
-        <v>46186</v>
-      </c>
-      <c r="Z25" s="9">
-        <v>46186</v>
-      </c>
-      <c r="AA25" s="9">
-        <v>46186</v>
-      </c>
-      <c r="AB25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD25" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="AE25" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF25" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG25" s="9">
-        <v>46142</v>
-      </c>
-      <c r="AH25" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" ht="28" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B26" s="15" t="s">
+      <c r="Z26" s="9">
+        <v>46149</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>46149</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD26" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="AE26" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="K26" s="5">
-        <v>250</v>
-      </c>
-      <c r="L26" s="5">
-        <v>250</v>
-      </c>
-      <c r="M26" s="5">
-        <v>0</v>
-      </c>
-      <c r="N26" s="6">
-        <v>18.2</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="P26" s="6">
-        <v>16.744</v>
-      </c>
-      <c r="Q26" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="R26" s="5">
-        <v>1.0874</v>
-      </c>
-      <c r="S26" s="6">
-        <v>18.207426</v>
-      </c>
-      <c r="T26" s="6">
-        <v>0.007426</v>
-      </c>
-      <c r="U26" s="7">
-        <v>0.000408021978021978</v>
-      </c>
-      <c r="V26" s="8">
-        <v>1.86</v>
-      </c>
-      <c r="W26" s="9">
-        <v>46205</v>
-      </c>
-      <c r="X26" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y26" s="9">
-        <v>46205</v>
-      </c>
-      <c r="Z26" s="9">
-        <v>46205</v>
-      </c>
-      <c r="AA26" s="9">
-        <v>46205</v>
-      </c>
-      <c r="AB26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD26" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="AE26" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="AF26" s="15" t="s">
-        <v>185</v>
-      </c>
+      <c r="AF26" s="13"/>
       <c r="AG26" s="9">
-        <v>46142</v>
-      </c>
-      <c r="AH26" s="15" t="s">
+        <v>46156</v>
+      </c>
+      <c r="AH26" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:34" ht="28" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>36</v>
@@ -5642,17 +6064,17 @@
         <v>38</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I27" s="15"/>
       <c r="J27" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K27" s="5">
         <v>2500</v>
@@ -5729,10 +6151,10 @@
     </row>
     <row r="28" spans="1:34" ht="28" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -5744,17 +6166,17 @@
         <v>38</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I28" s="15"/>
       <c r="J28" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K28" s="5">
         <v>1500</v>
@@ -5817,10 +6239,10 @@
         <v>0.99</v>
       </c>
       <c r="AE28" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AF28" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG28" s="9">
         <v>46158</v>
@@ -5831,10 +6253,10 @@
     </row>
     <row r="29" spans="1:34" ht="28" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -5856,7 +6278,7 @@
       </c>
       <c r="I29" s="15"/>
       <c r="J29" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K29" s="5">
         <v>200</v>
@@ -5919,10 +6341,10 @@
         <v>0.99</v>
       </c>
       <c r="AE29" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AF29" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG29" s="9">
         <v>46148</v>
@@ -5933,10 +6355,10 @@
     </row>
     <row r="30" spans="1:34" ht="28" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -5958,7 +6380,7 @@
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K30" s="5">
         <v>1500</v>
@@ -6021,10 +6443,10 @@
         <v>0.99</v>
       </c>
       <c r="AE30" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AF30" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG30" s="9">
         <v>46147</v>
@@ -6035,10 +6457,10 @@
     </row>
     <row r="31" spans="1:34" ht="28" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -6050,17 +6472,17 @@
         <v>38</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K31" s="5">
         <v>5000</v>
@@ -6123,10 +6545,10 @@
         <v>0.99</v>
       </c>
       <c r="AE31" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AF31" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG31" s="9">
         <v>46146</v>
@@ -6137,10 +6559,10 @@
     </row>
     <row r="32" spans="1:34" ht="28" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -6162,7 +6584,7 @@
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K32" s="5">
         <v>1000</v>
@@ -6225,10 +6647,10 @@
         <v>0.99</v>
       </c>
       <c r="AE32" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AF32" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG32" s="9">
         <v>46149</v>
@@ -6239,10 +6661,10 @@
     </row>
     <row r="33" spans="1:34" ht="28" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C33" s="2">
         <v>2</v>
@@ -6254,17 +6676,17 @@
         <v>38</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K33" s="5">
         <v>1000</v>
@@ -6327,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="AE33" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AF33" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG33" s="9">
         <v>46149</v>
@@ -6341,10 +6763,10 @@
     </row>
     <row r="34" spans="1:34" ht="28" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -6356,17 +6778,17 @@
         <v>90</v>
       </c>
       <c r="F34" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="I34" s="15"/>
       <c r="J34" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K34" s="5">
         <v>50000</v>
@@ -6423,16 +6845,16 @@
         <v>0</v>
       </c>
       <c r="AC34" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD34" s="5">
         <v>0.92</v>
       </c>
       <c r="AE34" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AF34" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG34" s="9">
         <v>46145</v>
@@ -6443,10 +6865,10 @@
     </row>
     <row r="35" spans="1:34" ht="28" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -6458,17 +6880,17 @@
         <v>90</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I35" s="15"/>
       <c r="J35" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K35" s="5">
         <v>25000</v>
@@ -6531,10 +6953,10 @@
         <v>0.9</v>
       </c>
       <c r="AE35" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AF35" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG35" s="9">
         <v>46154</v>
@@ -6545,10 +6967,10 @@
     </row>
     <row r="36" spans="1:34" ht="28" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -6560,17 +6982,17 @@
         <v>90</v>
       </c>
       <c r="F36" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="I36" s="15"/>
       <c r="J36" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K36" s="5">
         <v>5000</v>
@@ -6627,16 +7049,16 @@
         <v>0</v>
       </c>
       <c r="AC36" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD36" s="5">
         <v>0.92</v>
       </c>
       <c r="AE36" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AF36" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG36" s="9">
         <v>46152</v>
@@ -6647,10 +7069,10 @@
     </row>
     <row r="37" spans="1:34" ht="28" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
@@ -6662,17 +7084,17 @@
         <v>90</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I37" s="15"/>
       <c r="J37" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K37" s="5">
         <v>25000</v>
@@ -6735,10 +7157,10 @@
         <v>0.9</v>
       </c>
       <c r="AE37" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AF37" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG37" s="9">
         <v>46152</v>
@@ -6749,10 +7171,10 @@
     </row>
     <row r="38" spans="1:34" ht="28" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C38" s="2">
         <v>3</v>
@@ -6764,17 +7186,17 @@
         <v>90</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I38" s="15"/>
       <c r="J38" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K38" s="5">
         <v>25000</v>
@@ -6837,10 +7259,10 @@
         <v>0.9</v>
       </c>
       <c r="AE38" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AF38" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG38" s="9">
         <v>46152</v>
@@ -6851,10 +7273,10 @@
     </row>
     <row r="39" spans="1:34" ht="28" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -6866,17 +7288,17 @@
         <v>90</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I39" s="15"/>
       <c r="J39" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K39" s="5">
         <v>25000</v>
@@ -6939,10 +7361,10 @@
         <v>0.9</v>
       </c>
       <c r="AE39" s="15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AF39" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG39" s="9">
         <v>46150</v>
@@ -6953,10 +7375,10 @@
     </row>
     <row r="40" spans="1:34" ht="28" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C40" s="2">
         <v>2</v>
@@ -6968,17 +7390,17 @@
         <v>90</v>
       </c>
       <c r="F40" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="I40" s="15"/>
       <c r="J40" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K40" s="5">
         <v>5000</v>
@@ -7035,16 +7457,16 @@
         <v>0</v>
       </c>
       <c r="AC40" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD40" s="5">
         <v>0.92</v>
       </c>
       <c r="AE40" s="15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AF40" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG40" s="9">
         <v>46150</v>
@@ -7055,10 +7477,10 @@
     </row>
     <row r="41" spans="1:34" ht="28" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -7070,17 +7492,17 @@
         <v>90</v>
       </c>
       <c r="F41" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="I41" s="15"/>
       <c r="J41" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K41" s="5">
         <v>25000</v>
@@ -7137,16 +7559,16 @@
         <v>0</v>
       </c>
       <c r="AC41" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD41" s="5">
         <v>0.92</v>
       </c>
       <c r="AE41" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AF41" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG41" s="9">
         <v>46144</v>
@@ -7157,10 +7579,10 @@
     </row>
     <row r="42" spans="1:34" ht="28" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C42" s="2">
         <v>2</v>
@@ -7172,17 +7594,17 @@
         <v>90</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I42" s="15"/>
       <c r="J42" s="15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K42" s="5">
         <v>25000</v>
@@ -7245,10 +7667,10 @@
         <v>0.9</v>
       </c>
       <c r="AE42" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AF42" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG42" s="9">
         <v>46144</v>
@@ -7259,10 +7681,10 @@
     </row>
     <row r="43" spans="1:34" ht="28" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C43" s="2">
         <v>3</v>
@@ -7274,17 +7696,17 @@
         <v>90</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I43" s="15"/>
       <c r="J43" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K43" s="5">
         <v>10000</v>
@@ -7347,10 +7769,10 @@
         <v>0.9</v>
       </c>
       <c r="AE43" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AF43" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG43" s="9">
         <v>46144</v>
@@ -7361,10 +7783,10 @@
     </row>
     <row r="44" spans="1:34" ht="28" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -7386,7 +7808,7 @@
       </c>
       <c r="I44" s="15"/>
       <c r="J44" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K44" s="5">
         <v>25000</v>
@@ -7449,10 +7871,10 @@
         <v>0.8</v>
       </c>
       <c r="AE44" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AF44" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG44" s="9">
         <v>46155</v>
@@ -7463,10 +7885,10 @@
     </row>
     <row r="45" spans="1:34" ht="28" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C45" s="2">
         <v>2</v>
@@ -7478,17 +7900,17 @@
         <v>90</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I45" s="15"/>
       <c r="J45" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K45" s="5">
         <v>25000</v>
@@ -7551,10 +7973,10 @@
         <v>0.9</v>
       </c>
       <c r="AE45" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AF45" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG45" s="9">
         <v>46155</v>
@@ -7565,10 +7987,10 @@
     </row>
     <row r="46" spans="1:34" ht="28" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2">
         <v>3</v>
@@ -7580,17 +8002,17 @@
         <v>90</v>
       </c>
       <c r="F46" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="H46" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="I46" s="15"/>
       <c r="J46" s="15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K46" s="5">
         <v>5000</v>
@@ -7647,16 +8069,16 @@
         <v>0</v>
       </c>
       <c r="AC46" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD46" s="5">
         <v>0.92</v>
       </c>
       <c r="AE46" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AF46" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG46" s="9">
         <v>46155</v>
@@ -7745,99 +8167,99 @@
   <sheetData>
     <row r="1" spans="1:20" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F2" s="9">
         <v>46148</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
@@ -7848,13 +8270,13 @@
         <v>1</v>
       </c>
       <c r="P2" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R2" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
@@ -7864,10 +8286,10 @@
         <v>44</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>36</v>
@@ -7879,19 +8301,19 @@
         <v>46159</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
@@ -7902,13 +8324,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q3" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R3" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
@@ -7918,10 +8340,10 @@
         <v>52</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>47</v>
@@ -7933,19 +8355,19 @@
         <v>46157</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
@@ -7956,50 +8378,50 @@
         <v>1</v>
       </c>
       <c r="P4" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q4" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R4" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
     </row>
     <row r="5" spans="1:20" ht="18" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F5" s="9">
         <v>46149</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
@@ -8010,50 +8432,50 @@
         <v>2</v>
       </c>
       <c r="P5" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R5" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R5" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:20" ht="18" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" s="9">
         <v>46159</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="16"/>
@@ -8064,50 +8486,50 @@
         <v>1</v>
       </c>
       <c r="P6" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R6" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R6" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S6" s="16"/>
       <c r="T6" s="16"/>
     </row>
     <row r="7" spans="1:20" ht="18" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F7" s="9">
         <v>46146</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
@@ -8118,50 +8540,50 @@
         <v>1</v>
       </c>
       <c r="P7" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R7" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R7" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
     </row>
     <row r="8" spans="1:20" ht="18" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F8" s="9">
         <v>46158</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
@@ -8172,50 +8594,50 @@
         <v>1</v>
       </c>
       <c r="P8" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R8" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R8" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S8" s="16"/>
       <c r="T8" s="16"/>
     </row>
     <row r="9" spans="1:20" ht="18" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F9" s="9">
         <v>46147</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
@@ -8226,50 +8648,50 @@
         <v>1</v>
       </c>
       <c r="P9" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R9" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
     </row>
     <row r="10" spans="1:20" ht="18" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>66</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F10" s="9">
         <v>46157</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
@@ -8280,50 +8702,48 @@
         <v>1</v>
       </c>
       <c r="P10" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R10" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R10" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
     </row>
     <row r="11" spans="1:20" ht="18" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>87</v>
-      </c>
+      <c r="E11" s="16"/>
       <c r="F11" s="9">
         <v>46156</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
@@ -8335,49 +8755,45 @@
         <v>285</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="S11" s="16" t="s">
-        <v>286</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="S11" s="16"/>
       <c r="T11" s="16"/>
     </row>
     <row r="12" spans="1:20" ht="18" customHeight="1">
       <c r="A12" s="16" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>171</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="E12" s="16"/>
       <c r="F12" s="9">
         <v>46156</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
@@ -8389,49 +8805,47 @@
         <v>285</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R12" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="S12" s="16" t="s">
-        <v>286</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="S12" s="16"/>
       <c r="T12" s="16"/>
     </row>
     <row r="13" spans="1:20" ht="18" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F13" s="9">
         <v>46158</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
@@ -8443,49 +8857,47 @@
         <v>285</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="S13" s="16" t="s">
-        <v>286</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="S13" s="16"/>
       <c r="T13" s="16"/>
     </row>
     <row r="14" spans="1:20" ht="18" customHeight="1">
       <c r="A14" s="16" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F14" s="9">
         <v>46154</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -8497,49 +8909,47 @@
         <v>285</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="S14" s="16" t="s">
-        <v>286</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="S14" s="16"/>
       <c r="T14" s="16"/>
     </row>
     <row r="15" spans="1:20" ht="18" customHeight="1">
       <c r="A15" s="16" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F15" s="9">
         <v>46145</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
@@ -8550,50 +8960,50 @@
         <v>1</v>
       </c>
       <c r="P15" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R15" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R15" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
     </row>
     <row r="16" spans="1:20" ht="18" customHeight="1">
       <c r="A16" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F16" s="9">
         <v>46155</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I16" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
@@ -8604,50 +9014,50 @@
         <v>3</v>
       </c>
       <c r="P16" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R16" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q16" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R16" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
     </row>
     <row r="17" spans="1:20" ht="18" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F17" s="9">
         <v>46150</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
@@ -8658,50 +9068,50 @@
         <v>2</v>
       </c>
       <c r="P17" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R17" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q17" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R17" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
     </row>
     <row r="18" spans="1:20" ht="18" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F18" s="9">
         <v>46154</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
@@ -8712,50 +9122,50 @@
         <v>1</v>
       </c>
       <c r="P18" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R18" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q18" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
     </row>
     <row r="19" spans="1:20" ht="18" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F19" s="9">
         <v>46144</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
@@ -8766,13 +9176,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R19" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
@@ -8782,7 +9192,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>89</v>
@@ -8797,19 +9207,19 @@
         <v>46153</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I20" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
@@ -8820,50 +9230,50 @@
         <v>1</v>
       </c>
       <c r="P20" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R20" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q20" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R20" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
     </row>
     <row r="21" spans="1:20" ht="18" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F21" s="9">
         <v>46152</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
@@ -8874,13 +9284,13 @@
         <v>3</v>
       </c>
       <c r="P21" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R21" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q21" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R21" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
@@ -8890,7 +9300,7 @@
         <v>105</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>100</v>
@@ -8899,25 +9309,25 @@
         <v>99</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F22" s="9">
         <v>46155</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L22" s="16">
         <v>1</v>
@@ -8930,25 +9340,23 @@
         <v>1</v>
       </c>
       <c r="P22" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R22" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="Q22" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R22" s="16" t="s">
-        <v>275</v>
-      </c>
       <c r="S22" s="16"/>
-      <c r="T22" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="T22" s="16"/>
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>100</v>
@@ -8963,19 +9371,19 @@
         <v>46158</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L23" s="16">
         <v>2</v>
@@ -8988,25 +9396,23 @@
         <v>1</v>
       </c>
       <c r="P23" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R23" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="Q23" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R23" s="16" t="s">
-        <v>275</v>
-      </c>
       <c r="S23" s="16"/>
-      <c r="T23" s="16" t="s">
-        <v>303</v>
-      </c>
+      <c r="T23" s="16"/>
     </row>
     <row r="24" spans="1:20" ht="18" customHeight="1">
       <c r="A24" s="16" t="s">
         <v>110</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>100</v>
@@ -9021,19 +9427,19 @@
         <v>46153</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
@@ -9042,102 +9448,104 @@
         <v>0</v>
       </c>
       <c r="P24" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R24" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
     </row>
     <row r="25" spans="1:20" ht="18" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>100</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F25" s="9">
         <v>46157</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
+      <c r="N25" s="16" t="s">
+        <v>304</v>
+      </c>
       <c r="O25" s="16">
         <v>1</v>
       </c>
       <c r="P25" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R25" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q25" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R25" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
     </row>
     <row r="26" spans="1:20" ht="18" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>100</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F26" s="9">
         <v>46152</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I26" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
@@ -9146,117 +9554,121 @@
         <v>1</v>
       </c>
       <c r="P26" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R26" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q26" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R26" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>100</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F27" s="9">
         <v>46156</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I27" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
+      <c r="N27" s="16" t="s">
+        <v>304</v>
+      </c>
       <c r="O27" s="16">
         <v>1</v>
       </c>
       <c r="P27" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q27" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R27" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q27" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R27" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
     </row>
     <row r="28" spans="1:20" ht="18" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>100</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F28" s="9">
         <v>46156</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
+      <c r="N28" s="16" t="s">
+        <v>304</v>
+      </c>
       <c r="O28" s="16">
         <v>1</v>
       </c>
       <c r="P28" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q28" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R28" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q28" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R28" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
@@ -9266,7 +9678,7 @@
         <v>123</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>114</v>
@@ -9281,19 +9693,19 @@
         <v>46143</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
@@ -9304,50 +9716,50 @@
         <v>2</v>
       </c>
       <c r="P29" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R29" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q29" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R29" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
     </row>
     <row r="30" spans="1:20" ht="18" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="F30" s="9">
         <v>46149</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
@@ -9358,50 +9770,50 @@
         <v>2</v>
       </c>
       <c r="P30" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R30" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q30" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R30" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
     </row>
     <row r="31" spans="1:20" ht="18" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="F31" s="9">
         <v>46142</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
@@ -9412,50 +9824,50 @@
         <v>1</v>
       </c>
       <c r="P31" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q31" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R31" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q31" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R31" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
     </row>
     <row r="32" spans="1:20" ht="18" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="F32" s="9">
         <v>46142</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I32" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
@@ -9466,48 +9878,48 @@
         <v>1</v>
       </c>
       <c r="P32" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q32" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R32" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q32" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R32" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S32" s="16"/>
       <c r="T32" s="16"/>
     </row>
     <row r="33" spans="1:20" ht="18" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>55</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="9">
         <v>46148</v>
       </c>
       <c r="G33" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="H33" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>272</v>
-      </c>
       <c r="K33" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
@@ -9518,48 +9930,48 @@
         <v>1</v>
       </c>
       <c r="P33" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q33" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R33" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q33" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R33" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
     </row>
     <row r="34" spans="1:20" ht="18" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>55</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E34" s="16"/>
       <c r="F34" s="9">
         <v>46153</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I34" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
@@ -9570,13 +9982,13 @@
         <v>1</v>
       </c>
       <c r="P34" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q34" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R34" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q34" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R34" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -9586,7 +9998,7 @@
         <v>61</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>55</v>
@@ -9599,19 +10011,19 @@
         <v>46156</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="I35" s="16" t="s">
         <v>62</v>
       </c>
       <c r="J35" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
@@ -9622,48 +10034,48 @@
         <v>2</v>
       </c>
       <c r="P35" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q35" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R35" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q35" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R35" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
     </row>
     <row r="36" spans="1:20" ht="18" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>55</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E36" s="16"/>
       <c r="F36" s="9">
         <v>46152</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I36" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
@@ -9674,13 +10086,13 @@
         <v>1</v>
       </c>
       <c r="P36" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q36" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R36" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="Q36" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="R36" s="16" t="s">
-        <v>275</v>
       </c>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
@@ -9745,51 +10157,51 @@
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E2" s="16">
         <v>36</v>
@@ -9807,24 +10219,24 @@
         <v>46100</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E3" s="16">
         <v>44</v>
@@ -9842,24 +10254,24 @@
         <v>46115</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
@@ -9877,21 +10289,21 @@
         <v>46114</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>91</v>
@@ -9912,24 +10324,24 @@
         <v>46103</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E6" s="16">
         <v>41</v>
@@ -9947,24 +10359,24 @@
         <v>46112</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>114</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E7" s="16">
         <v>18</v>
@@ -9982,21 +10394,21 @@
         <v>46080</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>116</v>
@@ -10017,24 +10429,24 @@
         <v>46112</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>114</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E9" s="16">
         <v>17</v>
@@ -10052,15 +10464,15 @@
         <v>46105</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>89</v>
@@ -10083,24 +10495,24 @@
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>114</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E11" s="16">
         <v>1</v>
@@ -10114,10 +10526,10 @@
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -10150,28 +10562,28 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -10209,7 +10621,7 @@
         <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -10223,10 +10635,10 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -10246,25 +10658,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="18" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="19" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B5" s="16">
         <v>35</v>
@@ -10272,7 +10684,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="19" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B6" s="16">
         <v>32</v>
@@ -10280,7 +10692,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="19" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
@@ -10288,7 +10700,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="19" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
@@ -10296,7 +10708,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="19" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B9" s="16">
         <v>4</v>
@@ -10304,7 +10716,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="19" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B10" s="16">
         <v>35</v>
@@ -10312,7 +10724,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="19" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B11" s="16">
         <v>0</v>
@@ -10320,7 +10732,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="19" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B12" s="16">
         <v>0</v>
@@ -10328,7 +10740,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="19" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B13" s="16">
         <v>44</v>
@@ -10336,7 +10748,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="19" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B14" s="16">
         <v>40</v>
@@ -10344,7 +10756,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="19" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B15" s="16">
         <v>1</v>
@@ -10352,7 +10764,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="19" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B16" s="16">
         <v>10</v>
@@ -10360,15 +10772,15 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="19" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B17" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="19" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
@@ -10376,7 +10788,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="19" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B19" s="16">
         <v>0</v>
@@ -10384,51 +10796,51 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="19" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="19" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="18" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="18" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="18" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="18" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -10452,16 +10864,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="80" customHeight="1">
@@ -10475,10 +10887,10 @@
         <v>36</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="80" customHeight="1">
@@ -10492,10 +10904,10 @@
         <v>47</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="80" customHeight="1">
@@ -10509,10 +10921,10 @@
         <v>54</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="80" customHeight="1">
@@ -10526,15 +10938,15 @@
         <v>54</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="80" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>38</v>
@@ -10543,10 +10955,10 @@
         <v>66</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="80" customHeight="1">
@@ -10557,30 +10969,30 @@
         <v>38</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="80" customHeight="1">
       <c r="A8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>78</v>
-      </c>
       <c r="D8" s="16" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="80" customHeight="1">
@@ -10594,10 +11006,10 @@
         <v>88</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="80" customHeight="1">
@@ -10611,10 +11023,10 @@
         <v>99</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="80" customHeight="1">
@@ -10628,10 +11040,10 @@
         <v>107</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/output/lisa_reconciliation.xlsx
+++ b/output/lisa_reconciliation.xlsx
@@ -849,136 +849,136 @@
     <t>gpt-4o-mini</t>
   </si>
   <si>
+    <t>d41e5965ac0d</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>1e36a3bb8230</t>
+  </si>
+  <si>
+    <t>b109ebc6b485</t>
+  </si>
+  <si>
+    <t>527671baf80d</t>
+  </si>
+  <si>
+    <t>78e12caee3d0</t>
+  </si>
+  <si>
+    <t>3a93a05eccfb</t>
+  </si>
+  <si>
+    <t>498d9e57c248</t>
+  </si>
+  <si>
+    <t>666ddb95cb5e</t>
+  </si>
+  <si>
+    <t>171acbfe62b4</t>
+  </si>
+  <si>
+    <t>CONTINENTAL QUALITY HEAT TREAT</t>
+  </si>
+  <si>
+    <t>VISION</t>
+  </si>
+  <si>
+    <t>bccc160e1d7a</t>
+  </si>
+  <si>
+    <t>ce09a43a057d</t>
+  </si>
+  <si>
+    <t>0335b5f9c32c</t>
+  </si>
+  <si>
+    <t>955c6553efee</t>
+  </si>
+  <si>
+    <t>803cca7204dd</t>
+  </si>
+  <si>
+    <t>5c96fdc23f2b</t>
+  </si>
+  <si>
+    <t>da7824243c72</t>
+  </si>
+  <si>
+    <t>0f0f0358478e</t>
+  </si>
+  <si>
+    <t>33d82e21944f</t>
+  </si>
+  <si>
+    <t>22e8e11993b9</t>
+  </si>
+  <si>
+    <t>c4b891a575c5</t>
+  </si>
+  <si>
+    <t>LIB-PO-9240</t>
+  </si>
+  <si>
+    <t>liberty_02.pdf</t>
+  </si>
+  <si>
+    <t>064f140583b6</t>
+  </si>
+  <si>
+    <t>df73e325ff79</t>
+  </si>
+  <si>
+    <t>RECEIPT_ONLY</t>
+  </si>
+  <si>
+    <t>RECEIPT_ACKNOWLEDGED_NO_SCHEDULE</t>
+  </si>
+  <si>
+    <t>e091bfef23ea</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>e8a55dd92b82</t>
+  </si>
+  <si>
+    <t>57987fd5631a</t>
+  </si>
+  <si>
+    <t>cb089f26bc54</t>
+  </si>
+  <si>
+    <t>7824420c3184</t>
+  </si>
+  <si>
+    <t>7dbe09998647</t>
+  </si>
+  <si>
+    <t>9e089392ebf2</t>
+  </si>
+  <si>
+    <t>af20c417f7de</t>
+  </si>
+  <si>
+    <t>quickship_01.pdf</t>
+  </si>
+  <si>
+    <t>450c226ef559</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>8c7d47657ef5</t>
+  </si>
+  <si>
+    <t>REVISION</t>
+  </si>
+  <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>d41e5965ac0d</t>
-  </si>
-  <si>
-    <t>1e36a3bb8230</t>
-  </si>
-  <si>
-    <t>b109ebc6b485</t>
-  </si>
-  <si>
-    <t>527671baf80d</t>
-  </si>
-  <si>
-    <t>78e12caee3d0</t>
-  </si>
-  <si>
-    <t>3a93a05eccfb</t>
-  </si>
-  <si>
-    <t>498d9e57c248</t>
-  </si>
-  <si>
-    <t>666ddb95cb5e</t>
-  </si>
-  <si>
-    <t>171acbfe62b4</t>
-  </si>
-  <si>
-    <t>CONTINENTAL QUALITY HEAT TREAT</t>
-  </si>
-  <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>VISION</t>
-  </si>
-  <si>
-    <t>bccc160e1d7a</t>
-  </si>
-  <si>
-    <t>ce09a43a057d</t>
-  </si>
-  <si>
-    <t>0335b5f9c32c</t>
-  </si>
-  <si>
-    <t>955c6553efee</t>
-  </si>
-  <si>
-    <t>803cca7204dd</t>
-  </si>
-  <si>
-    <t>5c96fdc23f2b</t>
-  </si>
-  <si>
-    <t>da7824243c72</t>
-  </si>
-  <si>
-    <t>0f0f0358478e</t>
-  </si>
-  <si>
-    <t>33d82e21944f</t>
-  </si>
-  <si>
-    <t>22e8e11993b9</t>
-  </si>
-  <si>
-    <t>c4b891a575c5</t>
-  </si>
-  <si>
-    <t>LIB-PO-9240</t>
-  </si>
-  <si>
-    <t>liberty_02.pdf</t>
-  </si>
-  <si>
-    <t>064f140583b6</t>
-  </si>
-  <si>
-    <t>df73e325ff79</t>
-  </si>
-  <si>
-    <t>RECEIPT_ONLY</t>
-  </si>
-  <si>
-    <t>RECEIPT_ACKNOWLEDGED_NO_SCHEDULE</t>
-  </si>
-  <si>
-    <t>e091bfef23ea</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>e8a55dd92b82</t>
-  </si>
-  <si>
-    <t>57987fd5631a</t>
-  </si>
-  <si>
-    <t>cb089f26bc54</t>
-  </si>
-  <si>
-    <t>7824420c3184</t>
-  </si>
-  <si>
-    <t>7dbe09998647</t>
-  </si>
-  <si>
-    <t>9e089392ebf2</t>
-  </si>
-  <si>
-    <t>af20c417f7de</t>
-  </si>
-  <si>
-    <t>quickship_01.pdf</t>
-  </si>
-  <si>
-    <t>450c226ef559</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>8c7d47657ef5</t>
-  </si>
-  <si>
-    <t>REVISION</t>
   </si>
   <si>
     <t>e614ec5ee714</t>
@@ -8276,7 +8276,7 @@
         <v>272</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
@@ -8286,7 +8286,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>67</v>
@@ -8304,7 +8304,7 @@
         <v>268</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>46</v>
@@ -8330,7 +8330,7 @@
         <v>272</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
@@ -8384,7 +8384,7 @@
         <v>272</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
@@ -8438,7 +8438,7 @@
         <v>272</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
@@ -8492,7 +8492,7 @@
         <v>272</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S6" s="16"/>
       <c r="T6" s="16"/>
@@ -8546,7 +8546,7 @@
         <v>272</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
@@ -8600,7 +8600,7 @@
         <v>272</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S8" s="16"/>
       <c r="T8" s="16"/>
@@ -8654,7 +8654,7 @@
         <v>272</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
@@ -8708,7 +8708,7 @@
         <v>272</v>
       </c>
       <c r="R10" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
@@ -8734,7 +8734,7 @@
         <v>268</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>46</v>
@@ -8752,13 +8752,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q11" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
@@ -8768,7 +8768,7 @@
         <v>182</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>283</v>
@@ -8784,7 +8784,7 @@
         <v>268</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>46</v>
@@ -8802,13 +8802,13 @@
         <v>1</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q12" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R12" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
@@ -8818,7 +8818,7 @@
         <v>178</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>283</v>
@@ -8836,7 +8836,7 @@
         <v>268</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>46</v>
@@ -8854,13 +8854,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q13" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
@@ -8870,7 +8870,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>283</v>
@@ -8888,7 +8888,7 @@
         <v>268</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>46</v>
@@ -8906,13 +8906,13 @@
         <v>1</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q14" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S14" s="16"/>
       <c r="T14" s="16"/>
@@ -8922,7 +8922,7 @@
         <v>216</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>89</v>
@@ -8966,7 +8966,7 @@
         <v>272</v>
       </c>
       <c r="R15" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
@@ -8976,7 +8976,7 @@
         <v>245</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>89</v>
@@ -9020,7 +9020,7 @@
         <v>272</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
@@ -9030,7 +9030,7 @@
         <v>234</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>89</v>
@@ -9074,7 +9074,7 @@
         <v>272</v>
       </c>
       <c r="R17" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
@@ -9084,7 +9084,7 @@
         <v>222</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>89</v>
@@ -9128,7 +9128,7 @@
         <v>272</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
@@ -9138,7 +9138,7 @@
         <v>239</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>89</v>
@@ -9182,7 +9182,7 @@
         <v>272</v>
       </c>
       <c r="R19" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
@@ -9192,7 +9192,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>89</v>
@@ -9236,7 +9236,7 @@
         <v>272</v>
       </c>
       <c r="R20" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
@@ -9246,7 +9246,7 @@
         <v>226</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>89</v>
@@ -9290,7 +9290,7 @@
         <v>272</v>
       </c>
       <c r="R21" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
@@ -9300,7 +9300,7 @@
         <v>105</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>100</v>
@@ -9309,7 +9309,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F22" s="9">
         <v>46155</v>
@@ -9318,7 +9318,7 @@
         <v>268</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>46</v>
@@ -9346,17 +9346,17 @@
         <v>272</v>
       </c>
       <c r="R22" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1">
       <c r="A23" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>298</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>299</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>100</v>
@@ -9374,7 +9374,7 @@
         <v>268</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>46</v>
@@ -9402,7 +9402,7 @@
         <v>272</v>
       </c>
       <c r="R23" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
@@ -9412,7 +9412,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>100</v>
@@ -9427,10 +9427,10 @@
         <v>46153</v>
       </c>
       <c r="G24" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>301</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>302</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>46</v>
@@ -9454,7 +9454,7 @@
         <v>272</v>
       </c>
       <c r="R24" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
@@ -9464,7 +9464,7 @@
         <v>156</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>100</v>
@@ -9482,7 +9482,7 @@
         <v>268</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>46</v>
@@ -9496,7 +9496,7 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O25" s="16">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         <v>272</v>
       </c>
       <c r="R25" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
@@ -9518,7 +9518,7 @@
         <v>168</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>100</v>
@@ -9536,7 +9536,7 @@
         <v>268</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I26" s="16" t="s">
         <v>46</v>
@@ -9560,7 +9560,7 @@
         <v>272</v>
       </c>
       <c r="R26" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
@@ -9570,7 +9570,7 @@
         <v>160</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>100</v>
@@ -9588,7 +9588,7 @@
         <v>268</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I27" s="16" t="s">
         <v>46</v>
@@ -9602,7 +9602,7 @@
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
       <c r="N27" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O27" s="16">
         <v>1</v>
@@ -9614,7 +9614,7 @@
         <v>272</v>
       </c>
       <c r="R27" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
@@ -9624,7 +9624,7 @@
         <v>164</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>100</v>
@@ -9642,7 +9642,7 @@
         <v>268</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>46</v>
@@ -9656,7 +9656,7 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O28" s="16">
         <v>1</v>
@@ -9668,7 +9668,7 @@
         <v>272</v>
       </c>
       <c r="R28" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
@@ -9678,7 +9678,7 @@
         <v>123</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>114</v>
@@ -9696,7 +9696,7 @@
         <v>268</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>46</v>
@@ -9722,7 +9722,7 @@
         <v>272</v>
       </c>
       <c r="R29" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
@@ -9732,7 +9732,7 @@
         <v>129</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>114</v>
@@ -9776,7 +9776,7 @@
         <v>272</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
@@ -9786,7 +9786,7 @@
         <v>141</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>114</v>
@@ -9830,7 +9830,7 @@
         <v>272</v>
       </c>
       <c r="R31" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
@@ -9840,7 +9840,7 @@
         <v>137</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>114</v>
@@ -9884,17 +9884,17 @@
         <v>272</v>
       </c>
       <c r="R32" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S32" s="16"/>
       <c r="T32" s="16"/>
     </row>
     <row r="33" spans="1:20" ht="18" customHeight="1">
       <c r="A33" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>312</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>313</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>55</v>
@@ -9913,7 +9913,7 @@
         <v>269</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J33" s="16" t="s">
         <v>270</v>
@@ -9936,7 +9936,7 @@
         <v>272</v>
       </c>
       <c r="R33" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
@@ -9946,7 +9946,7 @@
         <v>146</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>55</v>
@@ -9959,7 +9959,7 @@
         <v>46153</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H34" s="16" t="s">
         <v>269</v>
@@ -9968,10 +9968,10 @@
         <v>46</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
@@ -9988,7 +9988,7 @@
         <v>272</v>
       </c>
       <c r="R34" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -10014,7 +10014,7 @@
         <v>318</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I35" s="16" t="s">
         <v>62</v>
@@ -10040,7 +10040,7 @@
         <v>272</v>
       </c>
       <c r="R35" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
@@ -10092,7 +10092,7 @@
         <v>272</v>
       </c>
       <c r="R36" s="16" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
@@ -10719,7 +10719,7 @@
         <v>358</v>
       </c>
       <c r="B10" s="16">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10727,7 +10727,7 @@
         <v>359</v>
       </c>
       <c r="B11" s="16">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/output/lisa_reconciliation.xlsx
+++ b/output/lisa_reconciliation.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ACTION_QUEUE!$A$1:$AI$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ALL_PO_LINES!$A$1:$AH$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DOCUMENTS!$A$1:$T$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">FOLLOW_UPS!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">FOLLOW_UPS!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PART_MAPPING!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">UNMATCHED_LINES!$A$1:$K$3</definedName>
   </definedNames>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="399">
   <si>
     <t>Priority</t>
   </si>
@@ -462,7 +462,7 @@
     <t>PO-4500050030</t>
   </si>
   <si>
-    <t>DOCUMENT_REVISION;DOCUMENT_SUPERSEDED;DATE_SEMANTICS_WARNING</t>
+    <t>DOCUMENT_REVISION;PRIOR_DOCUMENT_SUPERSEDED;DATE_SEMANTICS_WARNING</t>
   </si>
   <si>
     <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050030. Confirm whether the ship date will still meet the required date at Beacon.</t>
@@ -849,6 +849,9 @@
     <t>gpt-4o-mini</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>d41e5965ac0d</t>
   </si>
   <si>
@@ -976,9 +979,6 @@
   </si>
   <si>
     <t>REVISION</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>e614ec5ee714</t>
@@ -1178,7 +1178,7 @@
   <si>
     <t>Hello,
 We received your document for PO-4500050001.
-Beacon PO PO-4500050001 line 2 (BAR-A286-250, qty 1,500 if ordered, required 2026-06-10) does not appear on the acknowledgment. Please confirm this line.
+Beacon PO PO-4500050001 line 2 BAR-A286-250 (BAR-A286-250, qty 1,500 if ordered, required 2026-06-10) does not appear on the acknowledgment. Please confirm this line.
 Thank you.
 Lisa Morgan
 Purchasing, Beacon Fasteners</t>
@@ -1196,12 +1196,13 @@
 Purchasing, Beacon Fasteners</t>
   </si>
   <si>
-    <t>PO-4500050032 confirmation discrepancy</t>
+    <t>PO-4500050032 formal acknowledgment requested</t>
   </si>
   <si>
     <t>Hello,
 We received your document for PO-4500050032.
-We have shipment/invoice evidence for PO-4500050032 but no formal order acknowledgment. Please send a confirmation of quantity, price, and promise date.
+Beacon has an invoice or shipping document for PO-4500050032, but no formal order acknowledgment.
+Please confirm quantity, price, and commitment date for line 1 MISC-WAS-A25 and line 2 MISC-SPR-001.
 Thank you.
 Lisa Morgan
 Purchasing, Beacon Fasteners</t>
@@ -1267,7 +1268,7 @@
   <si>
     <t>Hello,
 We received your document for PO-4500050019.
-Please provide a committed quantity and promise date for PO-4500050019 line 1 (PLAT-PASV).
+Please provide a committed quantity and promise date for PO-4500050019 line 1 PLAT-PASV.
 Thank you.
 Lisa Morgan
 Purchasing, Beacon Fasteners</t>
@@ -8276,7 +8277,7 @@
         <v>272</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
@@ -8286,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>67</v>
@@ -8304,7 +8305,7 @@
         <v>268</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>46</v>
@@ -8330,7 +8331,7 @@
         <v>272</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
@@ -8340,7 +8341,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>67</v>
@@ -8384,7 +8385,7 @@
         <v>272</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
@@ -8394,7 +8395,7 @@
         <v>205</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>67</v>
@@ -8438,7 +8439,7 @@
         <v>272</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
@@ -8448,7 +8449,7 @@
         <v>77</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>67</v>
@@ -8492,7 +8493,7 @@
         <v>272</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S6" s="16"/>
       <c r="T6" s="16"/>
@@ -8502,7 +8503,7 @@
         <v>201</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>67</v>
@@ -8546,7 +8547,7 @@
         <v>272</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
@@ -8556,7 +8557,7 @@
         <v>189</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>67</v>
@@ -8600,7 +8601,7 @@
         <v>272</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S8" s="16"/>
       <c r="T8" s="16"/>
@@ -8610,7 +8611,7 @@
         <v>197</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>67</v>
@@ -8654,7 +8655,7 @@
         <v>272</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
@@ -8664,7 +8665,7 @@
         <v>70</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>67</v>
@@ -8708,7 +8709,7 @@
         <v>272</v>
       </c>
       <c r="R10" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
@@ -8718,10 +8719,10 @@
         <v>87</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>79</v>
@@ -8734,7 +8735,7 @@
         <v>268</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>46</v>
@@ -8752,13 +8753,13 @@
         <v>1</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q11" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
@@ -8768,10 +8769,10 @@
         <v>182</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>180</v>
@@ -8784,7 +8785,7 @@
         <v>268</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>46</v>
@@ -8802,13 +8803,13 @@
         <v>1</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q12" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R12" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
@@ -8818,10 +8819,10 @@
         <v>178</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>174</v>
@@ -8836,7 +8837,7 @@
         <v>268</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>46</v>
@@ -8854,13 +8855,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q13" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
@@ -8870,10 +8871,10 @@
         <v>172</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>170</v>
@@ -8888,7 +8889,7 @@
         <v>268</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>46</v>
@@ -8906,13 +8907,13 @@
         <v>1</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q14" s="16" t="s">
         <v>272</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S14" s="16"/>
       <c r="T14" s="16"/>
@@ -8922,7 +8923,7 @@
         <v>216</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>89</v>
@@ -8966,7 +8967,7 @@
         <v>272</v>
       </c>
       <c r="R15" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
@@ -8976,7 +8977,7 @@
         <v>245</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>89</v>
@@ -9020,7 +9021,7 @@
         <v>272</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
@@ -9030,7 +9031,7 @@
         <v>234</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>89</v>
@@ -9074,7 +9075,7 @@
         <v>272</v>
       </c>
       <c r="R17" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
@@ -9084,7 +9085,7 @@
         <v>222</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>89</v>
@@ -9128,7 +9129,7 @@
         <v>272</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
@@ -9138,7 +9139,7 @@
         <v>239</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>89</v>
@@ -9182,7 +9183,7 @@
         <v>272</v>
       </c>
       <c r="R19" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
@@ -9192,7 +9193,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>89</v>
@@ -9236,7 +9237,7 @@
         <v>272</v>
       </c>
       <c r="R20" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
@@ -9246,7 +9247,7 @@
         <v>226</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>89</v>
@@ -9290,7 +9291,7 @@
         <v>272</v>
       </c>
       <c r="R21" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
@@ -9300,7 +9301,7 @@
         <v>105</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>100</v>
@@ -9309,7 +9310,7 @@
         <v>99</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F22" s="9">
         <v>46155</v>
@@ -9318,7 +9319,7 @@
         <v>268</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>46</v>
@@ -9346,17 +9347,17 @@
         <v>272</v>
       </c>
       <c r="R22" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>100</v>
@@ -9374,7 +9375,7 @@
         <v>268</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>46</v>
@@ -9402,7 +9403,7 @@
         <v>272</v>
       </c>
       <c r="R23" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
@@ -9412,7 +9413,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>100</v>
@@ -9427,10 +9428,10 @@
         <v>46153</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>46</v>
@@ -9454,7 +9455,7 @@
         <v>272</v>
       </c>
       <c r="R24" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
@@ -9464,7 +9465,7 @@
         <v>156</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>100</v>
@@ -9482,7 +9483,7 @@
         <v>268</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>46</v>
@@ -9496,7 +9497,7 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O25" s="16">
         <v>1</v>
@@ -9508,7 +9509,7 @@
         <v>272</v>
       </c>
       <c r="R25" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
@@ -9518,7 +9519,7 @@
         <v>168</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>100</v>
@@ -9536,7 +9537,7 @@
         <v>268</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I26" s="16" t="s">
         <v>46</v>
@@ -9560,7 +9561,7 @@
         <v>272</v>
       </c>
       <c r="R26" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
@@ -9570,7 +9571,7 @@
         <v>160</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>100</v>
@@ -9588,7 +9589,7 @@
         <v>268</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I27" s="16" t="s">
         <v>46</v>
@@ -9602,7 +9603,7 @@
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
       <c r="N27" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O27" s="16">
         <v>1</v>
@@ -9614,7 +9615,7 @@
         <v>272</v>
       </c>
       <c r="R27" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
@@ -9624,7 +9625,7 @@
         <v>164</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>100</v>
@@ -9642,7 +9643,7 @@
         <v>268</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>46</v>
@@ -9656,7 +9657,7 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O28" s="16">
         <v>1</v>
@@ -9668,7 +9669,7 @@
         <v>272</v>
       </c>
       <c r="R28" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
@@ -9678,7 +9679,7 @@
         <v>123</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>114</v>
@@ -9696,7 +9697,7 @@
         <v>268</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>46</v>
@@ -9722,7 +9723,7 @@
         <v>272</v>
       </c>
       <c r="R29" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
@@ -9732,7 +9733,7 @@
         <v>129</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>114</v>
@@ -9776,7 +9777,7 @@
         <v>272</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
@@ -9786,7 +9787,7 @@
         <v>141</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>114</v>
@@ -9830,7 +9831,7 @@
         <v>272</v>
       </c>
       <c r="R31" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
@@ -9840,7 +9841,7 @@
         <v>137</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>114</v>
@@ -9884,17 +9885,17 @@
         <v>272</v>
       </c>
       <c r="R32" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S32" s="16"/>
       <c r="T32" s="16"/>
     </row>
     <row r="33" spans="1:20" ht="18" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>55</v>
@@ -9913,7 +9914,7 @@
         <v>269</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J33" s="16" t="s">
         <v>270</v>
@@ -9936,7 +9937,7 @@
         <v>272</v>
       </c>
       <c r="R33" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
@@ -9946,7 +9947,7 @@
         <v>146</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>55</v>
@@ -9959,7 +9960,7 @@
         <v>46153</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H34" s="16" t="s">
         <v>269</v>
@@ -9968,10 +9969,10 @@
         <v>46</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
@@ -9988,7 +9989,7 @@
         <v>272</v>
       </c>
       <c r="R34" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -10014,7 +10015,7 @@
         <v>318</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I35" s="16" t="s">
         <v>62</v>
@@ -10040,7 +10041,7 @@
         <v>272</v>
       </c>
       <c r="R35" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
@@ -10092,7 +10093,7 @@
         <v>272</v>
       </c>
       <c r="R36" s="16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
@@ -10719,7 +10720,7 @@
         <v>358</v>
       </c>
       <c r="B10" s="16">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10727,7 +10728,7 @@
         <v>359</v>
       </c>
       <c r="B11" s="16">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10850,7 +10851,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="28.7109375" customWidth="1"/>
@@ -10929,87 +10930,87 @@
     </row>
     <row r="5" spans="1:5" ht="80" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="80" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="80" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="80" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="80" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="80" customHeight="1">
@@ -11020,34 +11021,17 @@
         <v>101</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="80" customHeight="1">
-      <c r="A11" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="E11" s="16" t="s">
         <v>398</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/lisa_reconciliation.xlsx
+++ b/output/lisa_reconciliation.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="405">
   <si>
     <t>Priority</t>
   </si>
@@ -162,921 +162,927 @@
     <t>USD</t>
   </si>
   <si>
+    <t>data/confirmations/apex_02.pdf</t>
+  </si>
+  <si>
+    <t>APX-552544</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>PO-4500050007</t>
+  </si>
+  <si>
+    <t>QTY_SHORT</t>
+  </si>
+  <si>
+    <t>Resolve 75-unit short confirmation on PO-4500050007 line 1 (BAR-A286-250) before release.</t>
+  </si>
+  <si>
+    <t>PROMISE_DATE</t>
+  </si>
+  <si>
+    <t>EXACT_CUSTOMER_PN</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_03.pdf</t>
+  </si>
+  <si>
+    <t>APX-978346</t>
+  </si>
+  <si>
+    <t>PO-4500050032</t>
+  </si>
+  <si>
+    <t>QuickShip Industrial</t>
+  </si>
+  <si>
+    <t>orders@quickship-ind.com</t>
+  </si>
+  <si>
+    <t>MISC-WAS-A25</t>
+  </si>
+  <si>
+    <t>Washer, A286, 0.25</t>
+  </si>
+  <si>
+    <t>NO_FORMAL_ACK_FOUND;INVOICE_NOT_ACK</t>
+  </si>
+  <si>
+    <t>No formal acknowledgment found for PO-4500050032 line 1. Request an order confirmation (the invoice/shipping notice is not sufficient).</t>
+  </si>
+  <si>
+    <t>data/confirmations/quickship_03.pdf</t>
+  </si>
+  <si>
+    <t>INFORMATIONAL</t>
+  </si>
+  <si>
+    <t>MISC-SPR-001</t>
+  </si>
+  <si>
+    <t>Spring, comp, 0.250 OD</t>
+  </si>
+  <si>
+    <t>No formal acknowledgment found for PO-4500050032 line 2. Request an order confirmation (the invoice/shipping notice is not sufficient).</t>
+  </si>
+  <si>
+    <t>PO-4500060619</t>
+  </si>
+  <si>
+    <t>APEX BAR &amp; TUBE CO.</t>
+  </si>
+  <si>
+    <t>UNKNOWN_PO</t>
+  </si>
+  <si>
+    <t>Verify whether this acknowledgment belongs to Beacon and whether PO number PO-4500060619 is correct.</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_rogue.pdf</t>
+  </si>
+  <si>
+    <t>APX-334543</t>
+  </si>
+  <si>
+    <t>PO-4500050002</t>
+  </si>
+  <si>
+    <t>BAR-CRES-250</t>
+  </si>
+  <si>
+    <t>CRES 17-4 PH bar stock, 0.250 dia</t>
+  </si>
+  <si>
+    <t>PRICE_HIGH</t>
+  </si>
+  <si>
+    <t>Confirm acceptance of $0.0902/unit increase (~2.30%) on PO-4500050002 line 1.</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_05.pdf</t>
+  </si>
+  <si>
+    <t>APX-389235</t>
+  </si>
+  <si>
+    <t>PO-4500050022</t>
+  </si>
+  <si>
+    <t>Continental Quality Heat Treat</t>
+  </si>
+  <si>
+    <t>info@continentalqht.com</t>
+  </si>
+  <si>
+    <t>HT-PRECIP</t>
+  </si>
+  <si>
+    <t>Precipitation heat treat A286, per lb</t>
+  </si>
+  <si>
+    <t>PRICE_NOT_STATED;PROMISE_LATE</t>
+  </si>
+  <si>
+    <t>Ask Continental Quality Heat Treat whether required date 2026-05-21 can be recovered; current promise is 21 days late.</t>
+  </si>
+  <si>
+    <t>SINGLE_REMAINING_LINE</t>
+  </si>
+  <si>
+    <t>data/confirmations/continental_01.pdf</t>
+  </si>
+  <si>
+    <t>PO-4500050012</t>
+  </si>
+  <si>
+    <t>Heritage Cold Heading</t>
+  </si>
+  <si>
+    <t>sales@heritagecoldheading.com</t>
+  </si>
+  <si>
+    <t>CHB-9472-4</t>
+  </si>
+  <si>
+    <t>APH-441-OS</t>
+  </si>
+  <si>
+    <t>Cold-headed blank for HX-9472-4</t>
+  </si>
+  <si>
+    <t>PROMISE_LATE</t>
+  </si>
+  <si>
+    <t>Ask Heritage Cold Heading whether required date 2026-06-04 can be recovered; current promise is 14 days late.</t>
+  </si>
+  <si>
+    <t>RULE_BASED</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_06.pdf</t>
+  </si>
+  <si>
+    <t>HCH-74805</t>
+  </si>
+  <si>
+    <t>PO-4500050016</t>
+  </si>
+  <si>
+    <t>Liberty Surface Finishing</t>
+  </si>
+  <si>
+    <t>service@libertysurface.com</t>
+  </si>
+  <si>
+    <t>PLAT-PASV</t>
+  </si>
+  <si>
+    <t>Passivation per AMS 2700, per piece</t>
+  </si>
+  <si>
+    <t>Ask Liberty Surface Finishing whether required date 2026-05-17 can be recovered; current promise is 7 days late.</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_01.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-8573</t>
+  </si>
+  <si>
+    <t>PO-4500050019</t>
+  </si>
+  <si>
+    <t>PROMISE_MISSING</t>
+  </si>
+  <si>
+    <t>Request committed quantity and promise date for PO-4500050019 line 1 (PLAT-PASV).</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_03.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-9821</t>
+  </si>
+  <si>
+    <t>YELLOW</t>
+  </si>
+  <si>
+    <t>PO-4500050027</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH</t>
+  </si>
+  <si>
+    <t>vertrieb@ostmark-wzg.de</t>
+  </si>
+  <si>
+    <t>TOOL-DIE-9472</t>
+  </si>
+  <si>
+    <t>Heading die set, 9472 profile</t>
+  </si>
+  <si>
+    <t>PROMISE_WINDOW_STRADDLES_REQUIRED</t>
+  </si>
+  <si>
+    <t>Delivery window for PO-4500050027 line 1 straddles required date 2026-05-15. Ask Ostmark Werkzeug GmbH to commit a date on or before 2026-05-15.</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>DELIVERY_WINDOW</t>
+  </si>
+  <si>
+    <t>EXACT_VENDOR_PN_TO_BEACON_PN</t>
+  </si>
+  <si>
+    <t>data/confirmations/ostmark_01.pdf</t>
+  </si>
+  <si>
+    <t>OST-220844</t>
+  </si>
+  <si>
+    <t>PO-4500050029</t>
+  </si>
+  <si>
+    <t>DATE_SEMANTICS_WARNING</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050029. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>SHIP_DATE</t>
+  </si>
+  <si>
+    <t>data/confirmations/ostmark_02.pdf</t>
+  </si>
+  <si>
+    <t>OST-224427</t>
+  </si>
+  <si>
+    <t>TOOL-INS-CAR</t>
+  </si>
+  <si>
+    <t>OST-CAR-A-100</t>
+  </si>
+  <si>
+    <t>Carbide threading insert, A-series</t>
+  </si>
+  <si>
+    <t>Delivery window for PO-4500050027 line 2 straddles required date 2026-05-15. Ask Ostmark Werkzeug GmbH to commit a date on or before 2026-05-15.</t>
+  </si>
+  <si>
+    <t>PO-4500050028</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050028. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>data/confirmations/ostmark_04.pdf</t>
+  </si>
+  <si>
+    <t>OST-226935</t>
+  </si>
+  <si>
+    <t>PO-4500050026</t>
+  </si>
+  <si>
+    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050026. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>data/confirmations/ostmark_03.pdf</t>
+  </si>
+  <si>
+    <t>OST-229377</t>
+  </si>
+  <si>
+    <t>PO-4500050030</t>
+  </si>
+  <si>
+    <t>DOCUMENT_REVISION;PRIOR_DOCUMENT_SUPERSEDED;DATE_SEMANTICS_WARNING</t>
+  </si>
+  <si>
+    <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050030. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>data/confirmations/quickship_02.pdf</t>
+  </si>
+  <si>
+    <t>PO-4500050031</t>
+  </si>
+  <si>
+    <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050031. Confirm whether the ship date will still meet the required date at Beacon.</t>
+  </si>
+  <si>
+    <t>data/confirmations/quickship_04.pdf</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t>PO-4500050017</t>
+  </si>
+  <si>
+    <t>PLAT-CAD</t>
+  </si>
+  <si>
+    <t>Cadmium plating per QQ-P-416, per piece</t>
+  </si>
+  <si>
+    <t>PRICE_NOT_STATED</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050017 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_04.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-9182</t>
+  </si>
+  <si>
+    <t>PO-4500050018</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050018 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_06.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-9157</t>
+  </si>
+  <si>
+    <t>PO-4500050020</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050020 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_07.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-9815</t>
+  </si>
+  <si>
+    <t>PO-4500050021</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050021 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_05.pdf</t>
+  </si>
+  <si>
+    <t>LIB-PO-9126</t>
+  </si>
+  <si>
+    <t>PO-4500050023</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050023 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/continental_04.pdf</t>
+  </si>
+  <si>
+    <t>CQH-42657</t>
+  </si>
+  <si>
+    <t>PO-4500050024</t>
+  </si>
+  <si>
+    <t>HT-SOLN</t>
+  </si>
+  <si>
+    <t>Solution treat + age, per lb</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050024 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/continental_03.pdf</t>
+  </si>
+  <si>
+    <t>CQH-40704</t>
+  </si>
+  <si>
+    <t>PO-4500050025</t>
+  </si>
+  <si>
+    <t>Confirmation for PO-4500050025 line 1 omits price; do not treat this as price acceptance.</t>
+  </si>
+  <si>
+    <t>data/confirmations/continental_02.pdf</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>BAR-A286-375</t>
+  </si>
+  <si>
+    <t>A286 bar stock, 0.375 dia, mill-cert</t>
+  </si>
+  <si>
+    <t>Review PO-4500050001 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>PO-4500050003</t>
+  </si>
+  <si>
+    <t>Review PO-4500050003 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_07.pdf</t>
+  </si>
+  <si>
+    <t>APX-932684</t>
+  </si>
+  <si>
+    <t>PO-4500050004</t>
+  </si>
+  <si>
+    <t>Review PO-4500050004 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_01.pdf</t>
+  </si>
+  <si>
+    <t>APX-408970</t>
+  </si>
+  <si>
+    <t>PO-4500050005</t>
+  </si>
+  <si>
+    <t>Review PO-4500050005 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_08.pdf</t>
+  </si>
+  <si>
+    <t>APX-945201</t>
+  </si>
+  <si>
+    <t>PO-4500050006</t>
+  </si>
+  <si>
+    <t>Review PO-4500050006 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_06.pdf</t>
+  </si>
+  <si>
+    <t>APX-253836</t>
+  </si>
+  <si>
+    <t>PO-4500050008</t>
+  </si>
+  <si>
+    <t>Review PO-4500050008 line 1 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>data/confirmations/apex_04.pdf</t>
+  </si>
+  <si>
+    <t>APX-737955</t>
+  </si>
+  <si>
+    <t>BAR-TI64-188</t>
+  </si>
+  <si>
+    <t>Ti-6Al-4V bar stock, 0.188 dia</t>
+  </si>
+  <si>
+    <t>Review PO-4500050008 line 2 with Apex Bar &amp; Tube Co..</t>
+  </si>
+  <si>
+    <t>PO-4500050009</t>
+  </si>
+  <si>
+    <t>CHB-9472-3</t>
+  </si>
+  <si>
+    <t>APH-441</t>
+  </si>
+  <si>
+    <t>Cold-headed blank for HX-9472-3</t>
+  </si>
+  <si>
+    <t>Review PO-4500050009 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>APPROVED_VENDOR_CROSSWALK</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_01.pdf</t>
+  </si>
+  <si>
+    <t>HCH-75140</t>
+  </si>
+  <si>
+    <t>PO-4500050010</t>
+  </si>
+  <si>
+    <t>CHB-7715</t>
+  </si>
+  <si>
+    <t>Cold-headed blank for CSK-7715</t>
+  </si>
+  <si>
+    <t>Review PO-4500050010 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_04.pdf</t>
+  </si>
+  <si>
+    <t>HCH-77215</t>
+  </si>
+  <si>
+    <t>PO-4500050011</t>
+  </si>
+  <si>
+    <t>Review PO-4500050011 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_07.pdf</t>
+  </si>
+  <si>
+    <t>HCH-72939</t>
+  </si>
+  <si>
+    <t>CHB-3301</t>
+  </si>
+  <si>
+    <t>Cold-headed blank for NUT-3301-N</t>
+  </si>
+  <si>
+    <t>Review PO-4500050011 line 2 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>Review PO-4500050011 line 3 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>PO-4500050013</t>
+  </si>
+  <si>
+    <t>Review PO-4500050013 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_03.pdf</t>
+  </si>
+  <si>
+    <t>HCH-77346</t>
+  </si>
+  <si>
+    <t>Review PO-4500050013 line 2 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>PO-4500050014</t>
+  </si>
+  <si>
+    <t>Review PO-4500050014 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_05.pdf</t>
+  </si>
+  <si>
+    <t>HCH-78781</t>
+  </si>
+  <si>
+    <t>Review PO-4500050014 line 2 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>Review PO-4500050014 line 3 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>PO-4500050015</t>
+  </si>
+  <si>
+    <t>Review PO-4500050015 line 1 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>data/confirmations/heritage_02.pdf</t>
+  </si>
+  <si>
+    <t>HCH-75668</t>
+  </si>
+  <si>
+    <t>Review PO-4500050015 line 2 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>Review PO-4500050015 line 3 with Heritage Cold Heading.</t>
+  </si>
+  <si>
+    <t>Source File</t>
+  </si>
+  <si>
+    <t>SHA256</t>
+  </si>
+  <si>
+    <t>Vendor (raw)</t>
+  </si>
+  <si>
+    <t>Document Number</t>
+  </si>
+  <si>
+    <t>Document Type</t>
+  </si>
+  <si>
+    <t>Commitment Status</t>
+  </si>
+  <si>
+    <t>Lifecycle</t>
+  </si>
+  <si>
+    <t>Revision?</t>
+  </si>
+  <si>
+    <t>Supersedes prior?</t>
+  </si>
+  <si>
+    <t>Part N</t>
+  </si>
+  <si>
+    <t>Part M</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Line Count</t>
+  </si>
+  <si>
+    <t>Extraction Mode</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Cached?</t>
+  </si>
+  <si>
+    <t>Warnings</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>a2b124191abb</t>
+  </si>
+  <si>
+    <t>ACKNOWLEDGEMENT</t>
+  </si>
+  <si>
+    <t>FULL</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>NATIVE_TEXT</t>
+  </si>
+  <si>
+    <t>gpt-4o-mini</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>d41e5965ac0d</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>1e36a3bb8230</t>
+  </si>
+  <si>
+    <t>b109ebc6b485</t>
+  </si>
+  <si>
+    <t>527671baf80d</t>
+  </si>
+  <si>
+    <t>78e12caee3d0</t>
+  </si>
+  <si>
+    <t>3a93a05eccfb</t>
+  </si>
+  <si>
+    <t>498d9e57c248</t>
+  </si>
+  <si>
+    <t>666ddb95cb5e</t>
+  </si>
+  <si>
+    <t>171acbfe62b4</t>
+  </si>
+  <si>
+    <t>CONTINENTAL QUALITY HEAT TREAT</t>
+  </si>
+  <si>
+    <t>VISION</t>
+  </si>
+  <si>
+    <t>bccc160e1d7a</t>
+  </si>
+  <si>
+    <t>ce09a43a057d</t>
+  </si>
+  <si>
+    <t>0335b5f9c32c</t>
+  </si>
+  <si>
+    <t>955c6553efee</t>
+  </si>
+  <si>
+    <t>803cca7204dd</t>
+  </si>
+  <si>
+    <t>5c96fdc23f2b</t>
+  </si>
+  <si>
+    <t>da7824243c72</t>
+  </si>
+  <si>
+    <t>0f0f0358478e</t>
+  </si>
+  <si>
+    <t>33d82e21944f</t>
+  </si>
+  <si>
+    <t>22e8e11993b9</t>
+  </si>
+  <si>
+    <t>c4b891a575c5</t>
+  </si>
+  <si>
+    <t>LIB-PO-9240</t>
+  </si>
+  <si>
+    <t>data/confirmations/liberty_02.pdf</t>
+  </si>
+  <si>
+    <t>064f140583b6</t>
+  </si>
+  <si>
+    <t>df73e325ff79</t>
+  </si>
+  <si>
+    <t>RECEIPT_ONLY</t>
+  </si>
+  <si>
+    <t>RECEIPT_ACKNOWLEDGED_NO_SCHEDULE</t>
+  </si>
+  <si>
+    <t>e091bfef23ea</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>e8a55dd92b82</t>
+  </si>
+  <si>
+    <t>57987fd5631a</t>
+  </si>
+  <si>
+    <t>cb089f26bc54</t>
+  </si>
+  <si>
+    <t>7824420c3184</t>
+  </si>
+  <si>
+    <t>7dbe09998647</t>
+  </si>
+  <si>
+    <t>9e089392ebf2</t>
+  </si>
+  <si>
+    <t>af20c417f7de</t>
+  </si>
+  <si>
+    <t>data/confirmations/quickship_01.pdf</t>
+  </si>
+  <si>
+    <t>450c226ef559</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>8c7d47657ef5</t>
+  </si>
+  <si>
+    <t>REVISION</t>
+  </si>
+  <si>
+    <t>e614ec5ee714</t>
+  </si>
+  <si>
+    <t>INVOICE</t>
+  </si>
+  <si>
+    <t>013b7d72a0f6</t>
+  </si>
+  <si>
+    <t>Vendor ID</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Vendor PN</t>
+  </si>
+  <si>
+    <t>Beacon PN</t>
+  </si>
+  <si>
+    <t>Evidence Count</t>
+  </si>
+  <si>
+    <t>Vendor PN Total</t>
+  </si>
+  <si>
+    <t>Purity</t>
+  </si>
+  <si>
+    <t>First Seen</t>
+  </si>
+  <si>
+    <t>Last Seen</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>V002</t>
+  </si>
+  <si>
+    <t>APH-125</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>historical_confirmation</t>
+  </si>
+  <si>
+    <t>APH-318</t>
+  </si>
+  <si>
+    <t>APH-4411</t>
+  </si>
+  <si>
+    <t>K-1050</t>
+  </si>
+  <si>
+    <t>CHB-5520</t>
+  </si>
+  <si>
+    <t>V005</t>
+  </si>
+  <si>
+    <t>TOOL-PUNCH-STD</t>
+  </si>
+  <si>
+    <t>WZ-9472-DS</t>
+  </si>
+  <si>
+    <t>WZ-HM-EIN</t>
+  </si>
+  <si>
+    <t>PROPOSED</t>
+  </si>
+  <si>
+    <t>current_document_context</t>
+  </si>
+  <si>
+    <t>Customer PN</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
     <t>apex_02.pdf</t>
   </si>
   <si>
-    <t>APX-552544</t>
-  </si>
-  <si>
-    <t>ACTIVE</t>
-  </si>
-  <si>
-    <t>PO-4500050007</t>
-  </si>
-  <si>
-    <t>QTY_SHORT</t>
-  </si>
-  <si>
-    <t>Resolve 75-unit short confirmation on PO-4500050007 line 1 (BAR-A286-250) before release.</t>
-  </si>
-  <si>
-    <t>PROMISE_DATE</t>
-  </si>
-  <si>
-    <t>EXACT_CUSTOMER_PN</t>
-  </si>
-  <si>
-    <t>apex_03.pdf</t>
-  </si>
-  <si>
-    <t>APX-978346</t>
-  </si>
-  <si>
-    <t>PO-4500050032</t>
-  </si>
-  <si>
-    <t>QuickShip Industrial</t>
-  </si>
-  <si>
-    <t>orders@quickship-ind.com</t>
-  </si>
-  <si>
-    <t>MISC-WAS-A25</t>
-  </si>
-  <si>
-    <t>Washer, A286, 0.25</t>
-  </si>
-  <si>
-    <t>NO_FORMAL_ACK_FOUND;INVOICE_NOT_ACK</t>
-  </si>
-  <si>
-    <t>No formal acknowledgment found for PO-4500050032 line 1. Request an order confirmation (the invoice/shipping notice is not sufficient).</t>
-  </si>
-  <si>
-    <t>quickship_03.pdf</t>
-  </si>
-  <si>
-    <t>INFORMATIONAL</t>
-  </si>
-  <si>
-    <t>MISC-SPR-001</t>
-  </si>
-  <si>
-    <t>Spring, comp, 0.250 OD</t>
-  </si>
-  <si>
-    <t>No formal acknowledgment found for PO-4500050032 line 2. Request an order confirmation (the invoice/shipping notice is not sufficient).</t>
-  </si>
-  <si>
-    <t>PO-4500060619</t>
-  </si>
-  <si>
-    <t>APEX BAR &amp; TUBE CO.</t>
-  </si>
-  <si>
-    <t>UNKNOWN_PO</t>
-  </si>
-  <si>
-    <t>Verify whether this acknowledgment belongs to Beacon and whether PO number PO-4500060619 is correct.</t>
-  </si>
-  <si>
     <t>apex_rogue.pdf</t>
   </si>
   <si>
-    <t>APX-334543</t>
-  </si>
-  <si>
-    <t>PO-4500050002</t>
-  </si>
-  <si>
-    <t>BAR-CRES-250</t>
-  </si>
-  <si>
-    <t>CRES 17-4 PH bar stock, 0.250 dia</t>
-  </si>
-  <si>
-    <t>PRICE_HIGH</t>
-  </si>
-  <si>
-    <t>Confirm acceptance of $0.0902/unit increase (~2.30%) on PO-4500050002 line 1.</t>
-  </si>
-  <si>
-    <t>apex_05.pdf</t>
-  </si>
-  <si>
-    <t>APX-389235</t>
-  </si>
-  <si>
-    <t>PO-4500050022</t>
-  </si>
-  <si>
-    <t>Continental Quality Heat Treat</t>
-  </si>
-  <si>
-    <t>info@continentalqht.com</t>
-  </si>
-  <si>
-    <t>HT-PRECIP</t>
-  </si>
-  <si>
-    <t>Precipitation heat treat A286, per lb</t>
-  </si>
-  <si>
-    <t>PRICE_NOT_STATED;PROMISE_LATE</t>
-  </si>
-  <si>
-    <t>Ask Continental Quality Heat Treat whether required date 2026-05-21 can be recovered; current promise is 21 days late.</t>
-  </si>
-  <si>
-    <t>SINGLE_REMAINING_LINE</t>
-  </si>
-  <si>
-    <t>continental_01.pdf</t>
-  </si>
-  <si>
-    <t>PO-4500050012</t>
-  </si>
-  <si>
-    <t>Heritage Cold Heading</t>
-  </si>
-  <si>
-    <t>sales@heritagecoldheading.com</t>
-  </si>
-  <si>
-    <t>CHB-9472-4</t>
-  </si>
-  <si>
-    <t>APH-441-OS</t>
-  </si>
-  <si>
-    <t>Cold-headed blank for HX-9472-4</t>
-  </si>
-  <si>
-    <t>PROMISE_LATE</t>
-  </si>
-  <si>
-    <t>Ask Heritage Cold Heading whether required date 2026-06-04 can be recovered; current promise is 14 days late.</t>
-  </si>
-  <si>
-    <t>RULE_BASED</t>
-  </si>
-  <si>
-    <t>heritage_06.pdf</t>
-  </si>
-  <si>
-    <t>HCH-74805</t>
-  </si>
-  <si>
-    <t>PO-4500050016</t>
-  </si>
-  <si>
-    <t>Liberty Surface Finishing</t>
-  </si>
-  <si>
-    <t>service@libertysurface.com</t>
-  </si>
-  <si>
-    <t>PLAT-PASV</t>
-  </si>
-  <si>
-    <t>Passivation per AMS 2700, per piece</t>
-  </si>
-  <si>
-    <t>Ask Liberty Surface Finishing whether required date 2026-05-17 can be recovered; current promise is 7 days late.</t>
-  </si>
-  <si>
-    <t>liberty_01.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-8573</t>
-  </si>
-  <si>
-    <t>PO-4500050019</t>
-  </si>
-  <si>
-    <t>PROMISE_MISSING</t>
-  </si>
-  <si>
-    <t>Request committed quantity and promise date for PO-4500050019 line 1 (PLAT-PASV).</t>
-  </si>
-  <si>
-    <t>liberty_03.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-9821</t>
-  </si>
-  <si>
-    <t>YELLOW</t>
-  </si>
-  <si>
-    <t>PO-4500050027</t>
-  </si>
-  <si>
-    <t>Ostmark Werkzeug GmbH</t>
-  </si>
-  <si>
-    <t>vertrieb@ostmark-wzg.de</t>
-  </si>
-  <si>
-    <t>TOOL-DIE-9472</t>
-  </si>
-  <si>
-    <t>Heading die set, 9472 profile</t>
-  </si>
-  <si>
-    <t>PROMISE_WINDOW_STRADDLES_REQUIRED</t>
-  </si>
-  <si>
-    <t>Delivery window for PO-4500050027 line 1 straddles required date 2026-05-15. Ask Ostmark Werkzeug GmbH to commit a date on or before 2026-05-15.</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>DELIVERY_WINDOW</t>
-  </si>
-  <si>
-    <t>EXACT_VENDOR_PN_TO_BEACON_PN</t>
-  </si>
-  <si>
-    <t>ostmark_01.pdf</t>
-  </si>
-  <si>
-    <t>OST-220844</t>
-  </si>
-  <si>
-    <t>PO-4500050029</t>
-  </si>
-  <si>
-    <t>DATE_SEMANTICS_WARNING</t>
-  </si>
-  <si>
-    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050029. Confirm whether the ship date will still meet the required date at Beacon.</t>
-  </si>
-  <si>
-    <t>SHIP_DATE</t>
-  </si>
-  <si>
-    <t>ostmark_02.pdf</t>
-  </si>
-  <si>
-    <t>OST-224427</t>
-  </si>
-  <si>
-    <t>TOOL-INS-CAR</t>
-  </si>
-  <si>
-    <t>OST-CAR-A-100</t>
-  </si>
-  <si>
-    <t>Carbide threading insert, A-series</t>
-  </si>
-  <si>
-    <t>Delivery window for PO-4500050027 line 2 straddles required date 2026-05-15. Ask Ostmark Werkzeug GmbH to commit a date on or before 2026-05-15.</t>
-  </si>
-  <si>
-    <t>PO-4500050028</t>
-  </si>
-  <si>
-    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050028. Confirm whether the ship date will still meet the required date at Beacon.</t>
-  </si>
-  <si>
-    <t>ostmark_04.pdf</t>
-  </si>
-  <si>
-    <t>OST-226935</t>
-  </si>
-  <si>
-    <t>PO-4500050026</t>
-  </si>
-  <si>
-    <t>Ostmark Werkzeug GmbH stated a ship date (not a Beacon receipt/promise date) on PO-4500050026. Confirm whether the ship date will still meet the required date at Beacon.</t>
-  </si>
-  <si>
-    <t>ostmark_03.pdf</t>
-  </si>
-  <si>
-    <t>OST-229377</t>
-  </si>
-  <si>
-    <t>PO-4500050030</t>
-  </si>
-  <si>
-    <t>DOCUMENT_REVISION;PRIOR_DOCUMENT_SUPERSEDED;DATE_SEMANTICS_WARNING</t>
-  </si>
-  <si>
-    <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050030. Confirm whether the ship date will still meet the required date at Beacon.</t>
-  </si>
-  <si>
-    <t>quickship_02.pdf</t>
-  </si>
-  <si>
-    <t>PO-4500050031</t>
-  </si>
-  <si>
-    <t>QuickShip Industrial stated a ship date (not a Beacon receipt/promise date) on PO-4500050031. Confirm whether the ship date will still meet the required date at Beacon.</t>
-  </si>
-  <si>
-    <t>quickship_04.pdf</t>
-  </si>
-  <si>
-    <t>INFO</t>
-  </si>
-  <si>
-    <t>PO-4500050017</t>
-  </si>
-  <si>
-    <t>PLAT-CAD</t>
-  </si>
-  <si>
-    <t>Cadmium plating per QQ-P-416, per piece</t>
-  </si>
-  <si>
-    <t>PRICE_NOT_STATED</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050017 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>liberty_04.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-9182</t>
-  </si>
-  <si>
-    <t>PO-4500050018</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050018 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>liberty_06.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-9157</t>
-  </si>
-  <si>
-    <t>PO-4500050020</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050020 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>liberty_07.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-9815</t>
-  </si>
-  <si>
-    <t>PO-4500050021</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050021 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>liberty_05.pdf</t>
-  </si>
-  <si>
-    <t>LIB-PO-9126</t>
-  </si>
-  <si>
-    <t>PO-4500050023</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050023 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>continental_04.pdf</t>
-  </si>
-  <si>
-    <t>CQH-42657</t>
-  </si>
-  <si>
-    <t>PO-4500050024</t>
-  </si>
-  <si>
-    <t>HT-SOLN</t>
-  </si>
-  <si>
-    <t>Solution treat + age, per lb</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050024 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>continental_03.pdf</t>
-  </si>
-  <si>
-    <t>CQH-40704</t>
-  </si>
-  <si>
-    <t>PO-4500050025</t>
-  </si>
-  <si>
-    <t>Confirmation for PO-4500050025 line 1 omits price; do not treat this as price acceptance.</t>
-  </si>
-  <si>
-    <t>continental_02.pdf</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>BAR-A286-375</t>
-  </si>
-  <si>
-    <t>A286 bar stock, 0.375 dia, mill-cert</t>
-  </si>
-  <si>
-    <t>Review PO-4500050001 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>PO-4500050003</t>
-  </si>
-  <si>
-    <t>Review PO-4500050003 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>apex_07.pdf</t>
-  </si>
-  <si>
-    <t>APX-932684</t>
-  </si>
-  <si>
-    <t>PO-4500050004</t>
-  </si>
-  <si>
-    <t>Review PO-4500050004 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>apex_01.pdf</t>
-  </si>
-  <si>
-    <t>APX-408970</t>
-  </si>
-  <si>
-    <t>PO-4500050005</t>
-  </si>
-  <si>
-    <t>Review PO-4500050005 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>apex_08.pdf</t>
-  </si>
-  <si>
-    <t>APX-945201</t>
-  </si>
-  <si>
-    <t>PO-4500050006</t>
-  </si>
-  <si>
-    <t>Review PO-4500050006 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>apex_06.pdf</t>
-  </si>
-  <si>
-    <t>APX-253836</t>
-  </si>
-  <si>
-    <t>PO-4500050008</t>
-  </si>
-  <si>
-    <t>Review PO-4500050008 line 1 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>apex_04.pdf</t>
-  </si>
-  <si>
-    <t>APX-737955</t>
-  </si>
-  <si>
-    <t>BAR-TI64-188</t>
-  </si>
-  <si>
-    <t>Ti-6Al-4V bar stock, 0.188 dia</t>
-  </si>
-  <si>
-    <t>Review PO-4500050008 line 2 with Apex Bar &amp; Tube Co..</t>
-  </si>
-  <si>
-    <t>PO-4500050009</t>
-  </si>
-  <si>
-    <t>CHB-9472-3</t>
-  </si>
-  <si>
-    <t>APH-441</t>
-  </si>
-  <si>
-    <t>Cold-headed blank for HX-9472-3</t>
-  </si>
-  <si>
-    <t>Review PO-4500050009 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>APPROVED_VENDOR_CROSSWALK</t>
-  </si>
-  <si>
-    <t>heritage_01.pdf</t>
-  </si>
-  <si>
-    <t>HCH-75140</t>
-  </si>
-  <si>
-    <t>PO-4500050010</t>
-  </si>
-  <si>
-    <t>CHB-7715</t>
-  </si>
-  <si>
-    <t>Cold-headed blank for CSK-7715</t>
-  </si>
-  <si>
-    <t>Review PO-4500050010 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>heritage_04.pdf</t>
-  </si>
-  <si>
-    <t>HCH-77215</t>
-  </si>
-  <si>
-    <t>PO-4500050011</t>
-  </si>
-  <si>
-    <t>Review PO-4500050011 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>heritage_07.pdf</t>
-  </si>
-  <si>
-    <t>HCH-72939</t>
-  </si>
-  <si>
-    <t>CHB-3301</t>
-  </si>
-  <si>
-    <t>Cold-headed blank for NUT-3301-N</t>
-  </si>
-  <si>
-    <t>Review PO-4500050011 line 2 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>Review PO-4500050011 line 3 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>PO-4500050013</t>
-  </si>
-  <si>
-    <t>Review PO-4500050013 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>heritage_03.pdf</t>
-  </si>
-  <si>
-    <t>HCH-77346</t>
-  </si>
-  <si>
-    <t>Review PO-4500050013 line 2 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>PO-4500050014</t>
-  </si>
-  <si>
-    <t>Review PO-4500050014 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>heritage_05.pdf</t>
-  </si>
-  <si>
-    <t>HCH-78781</t>
-  </si>
-  <si>
-    <t>Review PO-4500050014 line 2 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>Review PO-4500050014 line 3 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>PO-4500050015</t>
-  </si>
-  <si>
-    <t>Review PO-4500050015 line 1 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>heritage_02.pdf</t>
-  </si>
-  <si>
-    <t>HCH-75668</t>
-  </si>
-  <si>
-    <t>Review PO-4500050015 line 2 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>Review PO-4500050015 line 3 with Heritage Cold Heading.</t>
-  </si>
-  <si>
-    <t>Source File</t>
-  </si>
-  <si>
-    <t>SHA256</t>
-  </si>
-  <si>
-    <t>Vendor (raw)</t>
-  </si>
-  <si>
-    <t>Document Number</t>
-  </si>
-  <si>
-    <t>Document Type</t>
-  </si>
-  <si>
-    <t>Commitment Status</t>
-  </si>
-  <si>
-    <t>Lifecycle</t>
-  </si>
-  <si>
-    <t>Revision?</t>
-  </si>
-  <si>
-    <t>Supersedes prior?</t>
-  </si>
-  <si>
-    <t>Part N</t>
-  </si>
-  <si>
-    <t>Part M</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Line Count</t>
-  </si>
-  <si>
-    <t>Extraction Mode</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Cached?</t>
-  </si>
-  <si>
-    <t>Warnings</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>a2b124191abb</t>
-  </si>
-  <si>
-    <t>ACKNOWLEDGEMENT</t>
-  </si>
-  <si>
-    <t>FULL</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>NATIVE_TEXT</t>
-  </si>
-  <si>
-    <t>gpt-4o-mini</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>d41e5965ac0d</t>
-  </si>
-  <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>1e36a3bb8230</t>
-  </si>
-  <si>
-    <t>b109ebc6b485</t>
-  </si>
-  <si>
-    <t>527671baf80d</t>
-  </si>
-  <si>
-    <t>78e12caee3d0</t>
-  </si>
-  <si>
-    <t>3a93a05eccfb</t>
-  </si>
-  <si>
-    <t>498d9e57c248</t>
-  </si>
-  <si>
-    <t>666ddb95cb5e</t>
-  </si>
-  <si>
-    <t>171acbfe62b4</t>
-  </si>
-  <si>
-    <t>CONTINENTAL QUALITY HEAT TREAT</t>
-  </si>
-  <si>
-    <t>VISION</t>
-  </si>
-  <si>
-    <t>bccc160e1d7a</t>
-  </si>
-  <si>
-    <t>ce09a43a057d</t>
-  </si>
-  <si>
-    <t>0335b5f9c32c</t>
-  </si>
-  <si>
-    <t>955c6553efee</t>
-  </si>
-  <si>
-    <t>803cca7204dd</t>
-  </si>
-  <si>
-    <t>5c96fdc23f2b</t>
-  </si>
-  <si>
-    <t>da7824243c72</t>
-  </si>
-  <si>
-    <t>0f0f0358478e</t>
-  </si>
-  <si>
-    <t>33d82e21944f</t>
-  </si>
-  <si>
-    <t>22e8e11993b9</t>
-  </si>
-  <si>
-    <t>c4b891a575c5</t>
-  </si>
-  <si>
-    <t>LIB-PO-9240</t>
-  </si>
-  <si>
-    <t>liberty_02.pdf</t>
-  </si>
-  <si>
-    <t>064f140583b6</t>
-  </si>
-  <si>
-    <t>df73e325ff79</t>
-  </si>
-  <si>
-    <t>RECEIPT_ONLY</t>
-  </si>
-  <si>
-    <t>RECEIPT_ACKNOWLEDGED_NO_SCHEDULE</t>
-  </si>
-  <si>
-    <t>e091bfef23ea</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>e8a55dd92b82</t>
-  </si>
-  <si>
-    <t>57987fd5631a</t>
-  </si>
-  <si>
-    <t>cb089f26bc54</t>
-  </si>
-  <si>
-    <t>7824420c3184</t>
-  </si>
-  <si>
-    <t>7dbe09998647</t>
-  </si>
-  <si>
-    <t>9e089392ebf2</t>
-  </si>
-  <si>
-    <t>af20c417f7de</t>
-  </si>
-  <si>
-    <t>quickship_01.pdf</t>
-  </si>
-  <si>
-    <t>450c226ef559</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>8c7d47657ef5</t>
-  </si>
-  <si>
-    <t>REVISION</t>
-  </si>
-  <si>
-    <t>e614ec5ee714</t>
-  </si>
-  <si>
-    <t>INVOICE</t>
-  </si>
-  <si>
-    <t>013b7d72a0f6</t>
-  </si>
-  <si>
-    <t>Vendor ID</t>
-  </si>
-  <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Vendor PN</t>
-  </si>
-  <si>
-    <t>Beacon PN</t>
-  </si>
-  <si>
-    <t>Evidence Count</t>
-  </si>
-  <si>
-    <t>Vendor PN Total</t>
-  </si>
-  <si>
-    <t>Purity</t>
-  </si>
-  <si>
-    <t>First Seen</t>
-  </si>
-  <si>
-    <t>Last Seen</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>V002</t>
-  </si>
-  <si>
-    <t>APH-125</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>historical_confirmation</t>
-  </si>
-  <si>
-    <t>APH-318</t>
-  </si>
-  <si>
-    <t>APH-4411</t>
-  </si>
-  <si>
-    <t>K-1050</t>
-  </si>
-  <si>
-    <t>CHB-5520</t>
-  </si>
-  <si>
-    <t>V005</t>
-  </si>
-  <si>
-    <t>TOOL-PUNCH-STD</t>
-  </si>
-  <si>
-    <t>WZ-9472-DS</t>
-  </si>
-  <si>
-    <t>WZ-HM-EIN</t>
-  </si>
-  <si>
-    <t>PROPOSED</t>
-  </si>
-  <si>
-    <t>current_document_context</t>
-  </si>
-  <si>
-    <t>Customer PN</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
     <t>Beacon Purchasing Copilot — Run Summary</t>
   </si>
   <si>
@@ -1104,13 +1110,22 @@
     <t>Scanned PDFs</t>
   </si>
   <si>
+    <t>OpenAI-backed documents</t>
+  </si>
+  <si>
+    <t>Native text + OpenAI (incl. cache)</t>
+  </si>
+  <si>
+    <t>Vision + OpenAI (incl. cache)</t>
+  </si>
+  <si>
+    <t>Fresh AI extractions this run</t>
+  </si>
+  <si>
     <t>Cached extractions</t>
   </si>
   <si>
-    <t>AI extractions</t>
-  </si>
-  <si>
-    <t>Local/OCR extractions</t>
+    <t>Local/OCR fallbacks</t>
   </si>
   <si>
     <t>Open PO lines</t>
@@ -1159,6 +1174,9 @@
   </si>
   <si>
     <t>QuickShip 'ship' dates are compared for visibility and flagged DATE_SEMANTICS_WARNING.</t>
+  </si>
+  <si>
+    <t>Cached OpenAI results still count as OpenAI-backed; Fresh AI extractions this run is the API-call count.</t>
   </si>
   <si>
     <t>Contact</t>
@@ -3629,26 +3647,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AI19"/>
-  <hyperlinks>
-    <hyperlink ref="AF2" r:id="rId1"/>
-    <hyperlink ref="AF3" r:id="rId2"/>
-    <hyperlink ref="AF4" r:id="rId3"/>
-    <hyperlink ref="AF5" r:id="rId4"/>
-    <hyperlink ref="AF6" r:id="rId5"/>
-    <hyperlink ref="AF7" r:id="rId6"/>
-    <hyperlink ref="AF8" r:id="rId7"/>
-    <hyperlink ref="AF9" r:id="rId8"/>
-    <hyperlink ref="AF10" r:id="rId9"/>
-    <hyperlink ref="AF11" r:id="rId10"/>
-    <hyperlink ref="AF12" r:id="rId11"/>
-    <hyperlink ref="AF13" r:id="rId12"/>
-    <hyperlink ref="AF14" r:id="rId13"/>
-    <hyperlink ref="AF15" r:id="rId14"/>
-    <hyperlink ref="AF16" r:id="rId15"/>
-    <hyperlink ref="AF17" r:id="rId16"/>
-    <hyperlink ref="AF18" r:id="rId17"/>
-    <hyperlink ref="AF19" r:id="rId18"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8090,53 +8088,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AH46"/>
-  <hyperlinks>
-    <hyperlink ref="AE2" r:id="rId1"/>
-    <hyperlink ref="AE3" r:id="rId2"/>
-    <hyperlink ref="AE4" r:id="rId3"/>
-    <hyperlink ref="AE5" r:id="rId4"/>
-    <hyperlink ref="AE6" r:id="rId5"/>
-    <hyperlink ref="AE7" r:id="rId6"/>
-    <hyperlink ref="AE8" r:id="rId7"/>
-    <hyperlink ref="AE9" r:id="rId8"/>
-    <hyperlink ref="AE10" r:id="rId9"/>
-    <hyperlink ref="AE11" r:id="rId10"/>
-    <hyperlink ref="AE12" r:id="rId11"/>
-    <hyperlink ref="AE13" r:id="rId12"/>
-    <hyperlink ref="AE14" r:id="rId13"/>
-    <hyperlink ref="AE15" r:id="rId14"/>
-    <hyperlink ref="AE16" r:id="rId15"/>
-    <hyperlink ref="AE17" r:id="rId16"/>
-    <hyperlink ref="AE18" r:id="rId17"/>
-    <hyperlink ref="AE19" r:id="rId18"/>
-    <hyperlink ref="AE20" r:id="rId19"/>
-    <hyperlink ref="AE21" r:id="rId20"/>
-    <hyperlink ref="AE22" r:id="rId21"/>
-    <hyperlink ref="AE23" r:id="rId22"/>
-    <hyperlink ref="AE24" r:id="rId23"/>
-    <hyperlink ref="AE25" r:id="rId24"/>
-    <hyperlink ref="AE26" r:id="rId25"/>
-    <hyperlink ref="AE27" r:id="rId26"/>
-    <hyperlink ref="AE28" r:id="rId27"/>
-    <hyperlink ref="AE29" r:id="rId28"/>
-    <hyperlink ref="AE30" r:id="rId29"/>
-    <hyperlink ref="AE31" r:id="rId30"/>
-    <hyperlink ref="AE32" r:id="rId31"/>
-    <hyperlink ref="AE33" r:id="rId32"/>
-    <hyperlink ref="AE34" r:id="rId33"/>
-    <hyperlink ref="AE35" r:id="rId34"/>
-    <hyperlink ref="AE36" r:id="rId35"/>
-    <hyperlink ref="AE37" r:id="rId36"/>
-    <hyperlink ref="AE38" r:id="rId37"/>
-    <hyperlink ref="AE39" r:id="rId38"/>
-    <hyperlink ref="AE40" r:id="rId39"/>
-    <hyperlink ref="AE41" r:id="rId40"/>
-    <hyperlink ref="AE42" r:id="rId41"/>
-    <hyperlink ref="AE43" r:id="rId42"/>
-    <hyperlink ref="AE44" r:id="rId43"/>
-    <hyperlink ref="AE45" r:id="rId44"/>
-    <hyperlink ref="AE46" r:id="rId45"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10100,43 +10051,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T36"/>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3"/>
-    <hyperlink ref="A5" r:id="rId4"/>
-    <hyperlink ref="A6" r:id="rId5"/>
-    <hyperlink ref="A7" r:id="rId6"/>
-    <hyperlink ref="A8" r:id="rId7"/>
-    <hyperlink ref="A9" r:id="rId8"/>
-    <hyperlink ref="A10" r:id="rId9"/>
-    <hyperlink ref="A11" r:id="rId10"/>
-    <hyperlink ref="A12" r:id="rId11"/>
-    <hyperlink ref="A13" r:id="rId12"/>
-    <hyperlink ref="A14" r:id="rId13"/>
-    <hyperlink ref="A15" r:id="rId14"/>
-    <hyperlink ref="A16" r:id="rId15"/>
-    <hyperlink ref="A17" r:id="rId16"/>
-    <hyperlink ref="A18" r:id="rId17"/>
-    <hyperlink ref="A19" r:id="rId18"/>
-    <hyperlink ref="A20" r:id="rId19"/>
-    <hyperlink ref="A21" r:id="rId20"/>
-    <hyperlink ref="A22" r:id="rId21"/>
-    <hyperlink ref="A23" r:id="rId22"/>
-    <hyperlink ref="A24" r:id="rId23"/>
-    <hyperlink ref="A25" r:id="rId24"/>
-    <hyperlink ref="A26" r:id="rId25"/>
-    <hyperlink ref="A27" r:id="rId26"/>
-    <hyperlink ref="A28" r:id="rId27"/>
-    <hyperlink ref="A29" r:id="rId28"/>
-    <hyperlink ref="A30" r:id="rId29"/>
-    <hyperlink ref="A31" r:id="rId30"/>
-    <hyperlink ref="A32" r:id="rId31"/>
-    <hyperlink ref="A33" r:id="rId32"/>
-    <hyperlink ref="A34" r:id="rId33"/>
-    <hyperlink ref="A35" r:id="rId34"/>
-    <hyperlink ref="A36" r:id="rId35"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10611,7 +10525,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>41</v>
@@ -10636,7 +10550,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>68</v>
@@ -10650,7 +10564,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -10659,25 +10573,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="18" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B5" s="16">
         <v>35</v>
@@ -10685,7 +10599,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="19" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B6" s="16">
         <v>32</v>
@@ -10693,7 +10607,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="19" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
@@ -10701,7 +10615,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
@@ -10709,7 +10623,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B9" s="16">
         <v>4</v>
@@ -10717,7 +10631,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="19" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B10" s="16">
         <v>35</v>
@@ -10725,63 +10639,63 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B11" s="16">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B12" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B13" s="16">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B14" s="16">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B15" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B16" s="16">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B17" s="16">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
@@ -10789,59 +10703,88 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B19" s="16">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="B20" s="16">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>272</v>
+        <v>371</v>
+      </c>
+      <c r="B21" s="16">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>270</v>
+        <v>372</v>
+      </c>
+      <c r="B22" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="18" t="s">
-        <v>374</v>
+        <v>376</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="18" t="s">
-        <v>375</v>
+      <c r="A28" s="19" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="18" t="s">
-        <v>376</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="18" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="18" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="18" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -10865,16 +10808,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="80" customHeight="1">
@@ -10888,10 +10831,10 @@
         <v>36</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="80" customHeight="1">
@@ -10905,10 +10848,10 @@
         <v>47</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="80" customHeight="1">
@@ -10922,10 +10865,10 @@
         <v>54</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="80" customHeight="1">
@@ -10939,10 +10882,10 @@
         <v>66</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="80" customHeight="1">
@@ -10956,10 +10899,10 @@
         <v>72</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="80" customHeight="1">
@@ -10973,10 +10916,10 @@
         <v>79</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="80" customHeight="1">
@@ -10990,10 +10933,10 @@
         <v>88</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="80" customHeight="1">
@@ -11007,10 +10950,10 @@
         <v>99</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="80" customHeight="1">
@@ -11024,10 +10967,10 @@
         <v>107</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
